--- a/repair/back/doc/estimate/defect.xlsx
+++ b/repair/back/doc/estimate/defect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seongjaehyeon/anb_origin2/repair/back/doc/estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{570CEA6B-32C3-5941-882F-507324241774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B05BBB-8155-9643-8198-0C5B7BEA0012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="19800" tabRatio="731" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17040" yWindow="680" windowWidth="17100" windowHeight="19800" tabRatio="731" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="21" r:id="rId1"/>
@@ -394,7 +394,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="166">
   <si>
     <t>공 급 가 액</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -709,18 +709,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">① 시설물명 : </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">② 위      치 : </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">③ 용      도 : </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">① 계약기간은 착수 일로부터 </t>
     </r>
@@ -800,9 +788,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공동주택</t>
-  </si>
-  <si>
     <t>인  원</t>
   </si>
   <si>
@@ -820,10 +805,6 @@
   <si>
     <t>㈜에이앤비 대표이사</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">           1. 귀 아파트(사)의 무궁한 발전을 기원합니다.</t>
-    <phoneticPr fontId="102" type="noConversion"/>
   </si>
   <si>
     <t>제    목 :</t>
@@ -853,15 +834,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(우) 16910     경기도 용인시 기흥구 마북로 159 (마북동)        전화: 031-283-3328        팩스: 031-284-3328</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>㈜  에  이  앤  비</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입주자대표회의</t>
   </si>
   <si>
     <t>효성뉴서울5차아파트</t>
@@ -1052,10 +1026,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>하자점검(조사) 용역</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>하자점검(조사)보고서 3부</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1139,10 +1109,6 @@
       </rPr>
       <t>보강 등의 방법을 제시함으로써 재해 및 재난을 예방하고 시설물의 효용증진과 공공의 안전을 확보하는데 그 목적이 있다.</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">④ 하자점검(조사) 대상시설물의 범위 : </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1262,44 +1228,6 @@
     <phoneticPr fontId="102" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">           4. 시설물 개요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">           5. 용역의 범위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">           7. 특이사항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">      </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="바탕체"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="바탕체"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>6. 용  역  비  :</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>전화 :</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1309,30 +1237,6 @@
   </si>
   <si>
     <t>팩스 :</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>㈜에이앤비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(이하 "수주자"라 한다)는 다음과 같이 계약을 체결한다.</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1432,14 +1336,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">「공동주택관리법」(이하 “공주법”이라 한다) 제6장 하자담보책임 제36조(하자담보책임)과 제37조(하자보수 등), 시행령 제36조(담보책임기간)과 제37조(하자의 범위)의 규정에 따라 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(이하 "발주자"라 한다)와 하자점검(조사)의 실시자인 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>① "수주자"는 하자점검(조사)을 수행함에 있어서 필요한 경우에는 공동주택관리법 제36, 37조에 따라 "발주자"에게 해당 시설물의 설계</t>
     </r>
@@ -1486,32 +1382,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">           3. 귀 아파트(사)에서 의뢰하신 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="바탕체"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">하자점검(조사) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="바탕체"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>건에 대한 견적서를 제출하오니 업무에 참고하시기 바랍니다.</t>
-    </r>
-    <phoneticPr fontId="102" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1. 직 접 인 건 비</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1522,10 +1392,6 @@
   <si>
     <t>나. 보고서 제출 3부</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">           2. 당 사는 경기도 용인시 기흥구 마북로 159, 한성프라자 207호에 위치한 업체로 시설물 안전진단(구조 안전진단), 안전점검(정밀, 정기), 건축물 하자점검(조사), 장기수선계획 조정(검토 포함), 시설물 유지보수(도장, 방수공사 등), 보수공사 감리, 기술자문 등을 주 업무로 하는 ㈜에이앤비입니다.</t>
-    <phoneticPr fontId="102" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">가. 조 사 대 상  : </t>
@@ -1553,6 +1419,212 @@
   </si>
   <si>
     <t>나. 내업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>1. 귀 아파트(사)의 무궁한 발전을 기원합니다.</t>
+    </r>
+    <phoneticPr fontId="102" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>2. 당 사는 경기도 용인시 기흥구 마북로 159, 한성프라자 207호에 위치한 업체로 시설물 안전진단(구조 안전진단), 안전점검(정밀, 정기), 건축물 하자점검(조사), 장기수선계획 조정(검토 포함), 시설물 유지보수(도장, 방수공사 등), 보수공사 감리, 기술자문 등을 주 업무로 하는 ㈜에이앤비입니다.</t>
+    </r>
+    <phoneticPr fontId="102" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">3. 귀 아파트(사)에서 의뢰하신 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">하자점검(조사) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건에 대한 견적서를 제출하오니 업무에 참고하시기 바랍니다.</t>
+    </r>
+    <phoneticPr fontId="102" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>4. 시설물 개요</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>5. 용역의 범위</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>7. 특이사항</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>6. 용  역  비  :</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>③ 용      도 : 공동주택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(우)16910  경기도 용인시 기흥구 마북로 159 한성프라자 207호 (마북동) 전화 : 031-283-3328  팩스 : 031-284-3328</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「공동주택관리법」(이하 “공주법”이라 한다) 제6장 하자담보책임 제36조(하자담보책임)과 제37조(하자보수 등), 시행령 제36조(담보책임기간)과 제37조(하자의 범위)의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜에이앤비(이하 "수주자"라 한다)는 다음과 같이 계약을 체결한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1633,7 +1705,7 @@
     <numFmt numFmtId="244" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="245" formatCode="0_ "/>
   </numFmts>
-  <fonts count="120">
+  <fonts count="119">
     <font>
       <sz val="11"/>
       <name val="돋움"/>
@@ -2325,14 +2397,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="돋움"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color indexed="8"/>
       <name val="돋움"/>
@@ -2399,10 +2463,11 @@
       <charset val="129"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="돋움"/>
-      <family val="3"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -9905,7 +9970,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="274">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3104" applyFont="1">
       <alignment vertical="center"/>
@@ -10257,34 +10322,429 @@
     <xf numFmtId="38" fontId="76" fillId="0" borderId="76" xfId="2792" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="3113" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="3113" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="118" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="118" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="93" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="245" fontId="107" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="71" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="72" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="7" borderId="59" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="7" borderId="60" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="75" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="49" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="7" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="7" borderId="73" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="7" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="68" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="69" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="70" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="71" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="6" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="54" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="71" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="72" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="2" borderId="59" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="2" borderId="60" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="75" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="8" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="8" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="49" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="7" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="73" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="68" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="69" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="2" borderId="21" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10315,408 +10775,6 @@
     </xf>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="8" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="8" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="49" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="7" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="75" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="49" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="7" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="73" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="68" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="69" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="73" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="68" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="69" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="70" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="71" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="6" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="54" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="71" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="72" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="2" borderId="59" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="2" borderId="60" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="75" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="71" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="72" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="59" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="60" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="245" fontId="107" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="93" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="114" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="114" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3119">
@@ -14974,36 +15032,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:29" s="37" customFormat="1" ht="42" customHeight="1">
-      <c r="B1" s="187" t="s">
-        <v>66</v>
+      <c r="B1" s="213" t="s">
+        <v>60</v>
       </c>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="187"/>
-      <c r="I1" s="187"/>
-      <c r="J1" s="187"/>
-      <c r="K1" s="187"/>
-      <c r="L1" s="187"/>
-      <c r="M1" s="187"/>
-      <c r="N1" s="187"/>
-      <c r="O1" s="187"/>
-      <c r="P1" s="187"/>
-      <c r="Q1" s="187"/>
-      <c r="R1" s="187"/>
-      <c r="S1" s="187"/>
-      <c r="T1" s="187"/>
-      <c r="U1" s="187"/>
-      <c r="V1" s="187"/>
-      <c r="W1" s="187"/>
-      <c r="X1" s="187"/>
-      <c r="Y1" s="187"/>
-      <c r="Z1" s="187"/>
-      <c r="AA1" s="187"/>
-      <c r="AB1" s="187"/>
-      <c r="AC1" s="187"/>
+      <c r="C1" s="213"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="213"/>
+      <c r="G1" s="213"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="213"/>
+      <c r="M1" s="213"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="213"/>
+      <c r="P1" s="213"/>
+      <c r="Q1" s="213"/>
+      <c r="R1" s="213"/>
+      <c r="S1" s="213"/>
+      <c r="T1" s="213"/>
+      <c r="U1" s="213"/>
+      <c r="V1" s="213"/>
+      <c r="W1" s="213"/>
+      <c r="X1" s="213"/>
+      <c r="Y1" s="213"/>
+      <c r="Z1" s="213"/>
+      <c r="AA1" s="213"/>
+      <c r="AB1" s="213"/>
+      <c r="AC1" s="213"/>
     </row>
     <row r="2" spans="2:29" s="37" customFormat="1" ht="12" customHeight="1">
       <c r="B2" s="38"/>
@@ -15036,36 +15094,36 @@
       <c r="AC2" s="40"/>
     </row>
     <row r="3" spans="2:29" s="37" customFormat="1" ht="18" customHeight="1">
-      <c r="B3" s="188" t="s">
-        <v>65</v>
+      <c r="B3" s="214" t="s">
+        <v>163</v>
       </c>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="188"/>
-      <c r="F3" s="188"/>
-      <c r="G3" s="188"/>
-      <c r="H3" s="188"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
-      <c r="L3" s="188"/>
-      <c r="M3" s="188"/>
-      <c r="N3" s="188"/>
-      <c r="O3" s="188"/>
-      <c r="P3" s="188"/>
-      <c r="Q3" s="188"/>
-      <c r="R3" s="188"/>
-      <c r="S3" s="188"/>
-      <c r="T3" s="188"/>
-      <c r="U3" s="188"/>
-      <c r="V3" s="188"/>
-      <c r="W3" s="188"/>
-      <c r="X3" s="188"/>
-      <c r="Y3" s="188"/>
-      <c r="Z3" s="188"/>
-      <c r="AA3" s="188"/>
-      <c r="AB3" s="188"/>
-      <c r="AC3" s="188"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
+      <c r="M3" s="214"/>
+      <c r="N3" s="214"/>
+      <c r="O3" s="214"/>
+      <c r="P3" s="214"/>
+      <c r="Q3" s="214"/>
+      <c r="R3" s="214"/>
+      <c r="S3" s="214"/>
+      <c r="T3" s="214"/>
+      <c r="U3" s="214"/>
+      <c r="V3" s="214"/>
+      <c r="W3" s="214"/>
+      <c r="X3" s="214"/>
+      <c r="Y3" s="214"/>
+      <c r="Z3" s="214"/>
+      <c r="AA3" s="214"/>
+      <c r="AB3" s="214"/>
+      <c r="AC3" s="214"/>
     </row>
     <row r="4" spans="2:29" s="37" customFormat="1" ht="7.5" customHeight="1">
       <c r="B4" s="45"/>
@@ -15128,14 +15186,14 @@
       <c r="AC5" s="40"/>
     </row>
     <row r="6" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B6" s="185" t="s">
-        <v>64</v>
+      <c r="B6" s="211" t="s">
+        <v>59</v>
       </c>
-      <c r="C6" s="185"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="185"/>
+      <c r="C6" s="211"/>
+      <c r="D6" s="211"/>
+      <c r="E6" s="211"/>
       <c r="F6" s="38" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G6" s="38"/>
       <c r="H6" s="38"/>
@@ -15162,27 +15220,27 @@
       <c r="AC6" s="40"/>
     </row>
     <row r="7" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B7" s="185" t="s">
-        <v>62</v>
+      <c r="B7" s="211" t="s">
+        <v>57</v>
       </c>
-      <c r="C7" s="185"/>
-      <c r="D7" s="185"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="189">
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+      <c r="F7" s="215">
         <v>46072</v>
       </c>
-      <c r="G7" s="189"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="189"/>
-      <c r="K7" s="189"/>
-      <c r="L7" s="189"/>
-      <c r="M7" s="189"/>
-      <c r="N7" s="189"/>
-      <c r="O7" s="189"/>
-      <c r="P7" s="189"/>
-      <c r="Q7" s="189"/>
-      <c r="R7" s="189"/>
+      <c r="G7" s="215"/>
+      <c r="H7" s="215"/>
+      <c r="I7" s="215"/>
+      <c r="J7" s="215"/>
+      <c r="K7" s="215"/>
+      <c r="L7" s="215"/>
+      <c r="M7" s="215"/>
+      <c r="N7" s="215"/>
+      <c r="O7" s="215"/>
+      <c r="P7" s="215"/>
+      <c r="Q7" s="215"/>
+      <c r="R7" s="215"/>
       <c r="S7" s="38"/>
       <c r="T7" s="38"/>
       <c r="U7" s="38"/>
@@ -15196,14 +15254,14 @@
       <c r="AC7" s="40"/>
     </row>
     <row r="8" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B8" s="185" t="s">
+      <c r="B8" s="211" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="211"/>
+      <c r="D8" s="211"/>
+      <c r="E8" s="211"/>
+      <c r="F8" s="119" t="s">
         <v>61</v>
-      </c>
-      <c r="C8" s="185"/>
-      <c r="D8" s="185"/>
-      <c r="E8" s="185"/>
-      <c r="F8" s="119" t="s">
-        <v>68</v>
       </c>
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
@@ -15212,9 +15270,7 @@
       <c r="K8" s="44"/>
       <c r="L8" s="44"/>
       <c r="M8" s="44"/>
-      <c r="N8" s="38" t="s">
-        <v>67</v>
-      </c>
+      <c r="N8" s="38"/>
       <c r="O8" s="38"/>
       <c r="P8" s="38"/>
       <c r="Q8" s="38"/>
@@ -15232,14 +15288,14 @@
       <c r="AC8" s="40"/>
     </row>
     <row r="9" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B9" s="185" t="s">
-        <v>60</v>
+      <c r="B9" s="211" t="s">
+        <v>55</v>
       </c>
-      <c r="C9" s="185"/>
-      <c r="D9" s="185"/>
-      <c r="E9" s="185"/>
+      <c r="C9" s="211"/>
+      <c r="D9" s="211"/>
+      <c r="E9" s="211"/>
       <c r="F9" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G9" s="38"/>
       <c r="H9" s="38"/>
@@ -15266,14 +15322,14 @@
       <c r="AC9" s="40"/>
     </row>
     <row r="10" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B10" s="185" t="s">
-        <v>58</v>
+      <c r="B10" s="211" t="s">
+        <v>53</v>
       </c>
-      <c r="C10" s="185"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
+      <c r="C10" s="211"/>
+      <c r="D10" s="211"/>
+      <c r="E10" s="211"/>
       <c r="F10" s="119" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
@@ -15390,36 +15446,36 @@
       <c r="AC13" s="40"/>
     </row>
     <row r="14" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B14" s="190" t="s">
-        <v>57</v>
+      <c r="B14" s="208" t="s">
+        <v>155</v>
       </c>
-      <c r="C14" s="190"/>
-      <c r="D14" s="190"/>
-      <c r="E14" s="190"/>
-      <c r="F14" s="190"/>
-      <c r="G14" s="190"/>
-      <c r="H14" s="190"/>
-      <c r="I14" s="190"/>
-      <c r="J14" s="190"/>
-      <c r="K14" s="190"/>
-      <c r="L14" s="190"/>
-      <c r="M14" s="190"/>
-      <c r="N14" s="190"/>
-      <c r="O14" s="190"/>
-      <c r="P14" s="190"/>
-      <c r="Q14" s="190"/>
-      <c r="R14" s="190"/>
-      <c r="S14" s="190"/>
-      <c r="T14" s="190"/>
-      <c r="U14" s="190"/>
-      <c r="V14" s="190"/>
-      <c r="W14" s="190"/>
-      <c r="X14" s="190"/>
-      <c r="Y14" s="190"/>
-      <c r="Z14" s="190"/>
-      <c r="AA14" s="190"/>
-      <c r="AB14" s="190"/>
-      <c r="AC14" s="190"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+      <c r="F14" s="208"/>
+      <c r="G14" s="208"/>
+      <c r="H14" s="208"/>
+      <c r="I14" s="208"/>
+      <c r="J14" s="208"/>
+      <c r="K14" s="208"/>
+      <c r="L14" s="208"/>
+      <c r="M14" s="208"/>
+      <c r="N14" s="208"/>
+      <c r="O14" s="208"/>
+      <c r="P14" s="208"/>
+      <c r="Q14" s="208"/>
+      <c r="R14" s="208"/>
+      <c r="S14" s="208"/>
+      <c r="T14" s="208"/>
+      <c r="U14" s="208"/>
+      <c r="V14" s="208"/>
+      <c r="W14" s="208"/>
+      <c r="X14" s="208"/>
+      <c r="Y14" s="208"/>
+      <c r="Z14" s="208"/>
+      <c r="AA14" s="208"/>
+      <c r="AB14" s="208"/>
+      <c r="AC14" s="208"/>
     </row>
     <row r="15" spans="2:29" s="37" customFormat="1" ht="10" customHeight="1">
       <c r="B15" s="114"/>
@@ -15452,36 +15508,36 @@
       <c r="AC15" s="116"/>
     </row>
     <row r="16" spans="2:29" s="37" customFormat="1" ht="70.5" customHeight="1">
-      <c r="B16" s="186" t="s">
-        <v>165</v>
+      <c r="B16" s="212" t="s">
+        <v>156</v>
       </c>
-      <c r="C16" s="186"/>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
-      <c r="F16" s="186"/>
-      <c r="G16" s="186"/>
-      <c r="H16" s="186"/>
-      <c r="I16" s="186"/>
-      <c r="J16" s="186"/>
-      <c r="K16" s="186"/>
-      <c r="L16" s="186"/>
-      <c r="M16" s="186"/>
-      <c r="N16" s="186"/>
-      <c r="O16" s="186"/>
-      <c r="P16" s="186"/>
-      <c r="Q16" s="186"/>
-      <c r="R16" s="186"/>
-      <c r="S16" s="186"/>
-      <c r="T16" s="186"/>
-      <c r="U16" s="186"/>
-      <c r="V16" s="186"/>
-      <c r="W16" s="186"/>
-      <c r="X16" s="186"/>
-      <c r="Y16" s="186"/>
-      <c r="Z16" s="186"/>
-      <c r="AA16" s="186"/>
-      <c r="AB16" s="186"/>
-      <c r="AC16" s="186"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="212"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="212"/>
+      <c r="I16" s="212"/>
+      <c r="J16" s="212"/>
+      <c r="K16" s="212"/>
+      <c r="L16" s="212"/>
+      <c r="M16" s="212"/>
+      <c r="N16" s="212"/>
+      <c r="O16" s="212"/>
+      <c r="P16" s="212"/>
+      <c r="Q16" s="212"/>
+      <c r="R16" s="212"/>
+      <c r="S16" s="212"/>
+      <c r="T16" s="212"/>
+      <c r="U16" s="212"/>
+      <c r="V16" s="212"/>
+      <c r="W16" s="212"/>
+      <c r="X16" s="212"/>
+      <c r="Y16" s="212"/>
+      <c r="Z16" s="212"/>
+      <c r="AA16" s="212"/>
+      <c r="AB16" s="212"/>
+      <c r="AC16" s="212"/>
     </row>
     <row r="17" spans="2:29" s="37" customFormat="1" ht="5" customHeight="1">
       <c r="B17" s="114"/>
@@ -15514,36 +15570,36 @@
       <c r="AC17" s="116"/>
     </row>
     <row r="18" spans="2:29" s="37" customFormat="1" ht="39" customHeight="1">
-      <c r="B18" s="186" t="s">
-        <v>161</v>
+      <c r="B18" s="212" t="s">
+        <v>157</v>
       </c>
-      <c r="C18" s="186"/>
-      <c r="D18" s="186"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="186"/>
-      <c r="G18" s="186"/>
-      <c r="H18" s="186"/>
-      <c r="I18" s="186"/>
-      <c r="J18" s="186"/>
-      <c r="K18" s="186"/>
-      <c r="L18" s="186"/>
-      <c r="M18" s="186"/>
-      <c r="N18" s="186"/>
-      <c r="O18" s="186"/>
-      <c r="P18" s="186"/>
-      <c r="Q18" s="186"/>
-      <c r="R18" s="186"/>
-      <c r="S18" s="186"/>
-      <c r="T18" s="186"/>
-      <c r="U18" s="186"/>
-      <c r="V18" s="186"/>
-      <c r="W18" s="186"/>
-      <c r="X18" s="186"/>
-      <c r="Y18" s="186"/>
-      <c r="Z18" s="186"/>
-      <c r="AA18" s="186"/>
-      <c r="AB18" s="186"/>
-      <c r="AC18" s="186"/>
+      <c r="C18" s="212"/>
+      <c r="D18" s="212"/>
+      <c r="E18" s="212"/>
+      <c r="F18" s="212"/>
+      <c r="G18" s="212"/>
+      <c r="H18" s="212"/>
+      <c r="I18" s="212"/>
+      <c r="J18" s="212"/>
+      <c r="K18" s="212"/>
+      <c r="L18" s="212"/>
+      <c r="M18" s="212"/>
+      <c r="N18" s="212"/>
+      <c r="O18" s="212"/>
+      <c r="P18" s="212"/>
+      <c r="Q18" s="212"/>
+      <c r="R18" s="212"/>
+      <c r="S18" s="212"/>
+      <c r="T18" s="212"/>
+      <c r="U18" s="212"/>
+      <c r="V18" s="212"/>
+      <c r="W18" s="212"/>
+      <c r="X18" s="212"/>
+      <c r="Y18" s="212"/>
+      <c r="Z18" s="212"/>
+      <c r="AA18" s="212"/>
+      <c r="AB18" s="212"/>
+      <c r="AC18" s="212"/>
     </row>
     <row r="19" spans="2:29" s="37" customFormat="1" ht="10" customHeight="1">
       <c r="B19" s="114"/>
@@ -15576,18 +15632,18 @@
       <c r="AC19" s="116"/>
     </row>
     <row r="20" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B20" s="190" t="s">
-        <v>138</v>
+      <c r="B20" s="208" t="s">
+        <v>158</v>
       </c>
-      <c r="C20" s="190"/>
-      <c r="D20" s="190"/>
-      <c r="E20" s="190"/>
-      <c r="F20" s="190"/>
-      <c r="G20" s="190"/>
-      <c r="H20" s="190"/>
-      <c r="I20" s="190"/>
-      <c r="J20" s="190"/>
-      <c r="K20" s="190"/>
+      <c r="C20" s="208"/>
+      <c r="D20" s="208"/>
+      <c r="E20" s="208"/>
+      <c r="F20" s="208"/>
+      <c r="G20" s="208"/>
+      <c r="H20" s="208"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="208"/>
       <c r="L20" s="38"/>
       <c r="M20" s="38"/>
       <c r="N20" s="38"/>
@@ -15612,17 +15668,16 @@
       <c r="C21" s="114"/>
       <c r="D21" s="114"/>
       <c r="E21" s="114"/>
-      <c r="F21" s="190" t="s">
-        <v>166</v>
+      <c r="F21" s="208" t="s">
+        <v>148</v>
       </c>
-      <c r="G21" s="190"/>
-      <c r="H21" s="190"/>
-      <c r="I21" s="190"/>
-      <c r="J21" s="190"/>
-      <c r="K21" s="190"/>
-      <c r="L21" s="120" t="str">
-        <f>F8</f>
-        <v>효성뉴서울5차아파트</v>
+      <c r="G21" s="208"/>
+      <c r="H21" s="208"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="208"/>
+      <c r="K21" s="208"/>
+      <c r="L21" s="120" t="s">
+        <v>61</v>
       </c>
       <c r="M21" s="120"/>
       <c r="N21" s="120"/>
@@ -15647,16 +15702,16 @@
       <c r="C22" s="114"/>
       <c r="D22" s="114"/>
       <c r="E22" s="114"/>
-      <c r="F22" s="190" t="s">
-        <v>167</v>
+      <c r="F22" s="208" t="s">
+        <v>149</v>
       </c>
-      <c r="G22" s="190"/>
-      <c r="H22" s="190"/>
-      <c r="I22" s="190"/>
-      <c r="J22" s="190"/>
-      <c r="K22" s="190"/>
+      <c r="G22" s="208"/>
+      <c r="H22" s="208"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="208"/>
+      <c r="K22" s="208"/>
       <c r="L22" s="120" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M22" s="120"/>
       <c r="N22" s="120"/>
@@ -15681,16 +15736,16 @@
       <c r="C23" s="114"/>
       <c r="D23" s="114"/>
       <c r="E23" s="114"/>
-      <c r="F23" s="190" t="s">
-        <v>168</v>
+      <c r="F23" s="208" t="s">
+        <v>150</v>
       </c>
-      <c r="G23" s="190"/>
-      <c r="H23" s="190"/>
-      <c r="I23" s="190"/>
-      <c r="J23" s="190"/>
-      <c r="K23" s="190"/>
+      <c r="G23" s="208"/>
+      <c r="H23" s="208"/>
+      <c r="I23" s="208"/>
+      <c r="J23" s="208"/>
+      <c r="K23" s="208"/>
       <c r="L23" s="120" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="M23" s="120"/>
       <c r="N23" s="120"/>
@@ -15715,16 +15770,16 @@
       <c r="C24" s="114"/>
       <c r="D24" s="114"/>
       <c r="E24" s="114"/>
-      <c r="F24" s="190" t="s">
-        <v>169</v>
+      <c r="F24" s="208" t="s">
+        <v>151</v>
       </c>
-      <c r="G24" s="190"/>
-      <c r="H24" s="190"/>
-      <c r="I24" s="190"/>
-      <c r="J24" s="190"/>
-      <c r="K24" s="190"/>
+      <c r="G24" s="208"/>
+      <c r="H24" s="208"/>
+      <c r="I24" s="208"/>
+      <c r="J24" s="208"/>
+      <c r="K24" s="208"/>
       <c r="L24" s="120" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="M24" s="120"/>
       <c r="N24" s="120"/>
@@ -15749,14 +15804,14 @@
       <c r="C25" s="114"/>
       <c r="D25" s="114"/>
       <c r="E25" s="114"/>
-      <c r="F25" s="190" t="s">
-        <v>170</v>
+      <c r="F25" s="208" t="s">
+        <v>152</v>
       </c>
-      <c r="G25" s="190"/>
-      <c r="H25" s="190"/>
-      <c r="I25" s="190"/>
-      <c r="J25" s="190"/>
-      <c r="K25" s="190"/>
+      <c r="G25" s="208"/>
+      <c r="H25" s="208"/>
+      <c r="I25" s="208"/>
+      <c r="J25" s="208"/>
+      <c r="K25" s="208"/>
       <c r="L25" s="120"/>
       <c r="M25" s="120"/>
       <c r="N25" s="120"/>
@@ -15807,18 +15862,18 @@
       <c r="AC26" s="116"/>
     </row>
     <row r="27" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B27" s="190" t="s">
-        <v>139</v>
+      <c r="B27" s="208" t="s">
+        <v>159</v>
       </c>
-      <c r="C27" s="190"/>
-      <c r="D27" s="190"/>
-      <c r="E27" s="190"/>
-      <c r="F27" s="190"/>
-      <c r="G27" s="190"/>
-      <c r="H27" s="190"/>
-      <c r="I27" s="190"/>
-      <c r="J27" s="190"/>
-      <c r="K27" s="190"/>
+      <c r="C27" s="208"/>
+      <c r="D27" s="208"/>
+      <c r="E27" s="208"/>
+      <c r="F27" s="208"/>
+      <c r="G27" s="208"/>
+      <c r="H27" s="208"/>
+      <c r="I27" s="208"/>
+      <c r="J27" s="208"/>
+      <c r="K27" s="208"/>
       <c r="L27" s="38"/>
       <c r="M27" s="38"/>
       <c r="N27" s="38"/>
@@ -15843,64 +15898,64 @@
       <c r="C28" s="114"/>
       <c r="D28" s="114"/>
       <c r="E28" s="114"/>
-      <c r="F28" s="193" t="s">
-        <v>121</v>
+      <c r="F28" s="209" t="s">
+        <v>112</v>
       </c>
-      <c r="G28" s="193"/>
-      <c r="H28" s="193"/>
-      <c r="I28" s="193"/>
-      <c r="J28" s="193"/>
-      <c r="K28" s="193"/>
-      <c r="L28" s="193"/>
-      <c r="M28" s="193"/>
-      <c r="N28" s="193"/>
-      <c r="O28" s="193"/>
-      <c r="P28" s="193"/>
-      <c r="Q28" s="193"/>
-      <c r="R28" s="193"/>
-      <c r="S28" s="193"/>
-      <c r="T28" s="193"/>
-      <c r="U28" s="193"/>
-      <c r="V28" s="193"/>
-      <c r="W28" s="193"/>
-      <c r="X28" s="193"/>
-      <c r="Y28" s="193"/>
-      <c r="Z28" s="193"/>
-      <c r="AA28" s="193"/>
-      <c r="AB28" s="193"/>
-      <c r="AC28" s="193"/>
+      <c r="G28" s="209"/>
+      <c r="H28" s="209"/>
+      <c r="I28" s="209"/>
+      <c r="J28" s="209"/>
+      <c r="K28" s="209"/>
+      <c r="L28" s="209"/>
+      <c r="M28" s="209"/>
+      <c r="N28" s="209"/>
+      <c r="O28" s="209"/>
+      <c r="P28" s="209"/>
+      <c r="Q28" s="209"/>
+      <c r="R28" s="209"/>
+      <c r="S28" s="209"/>
+      <c r="T28" s="209"/>
+      <c r="U28" s="209"/>
+      <c r="V28" s="209"/>
+      <c r="W28" s="209"/>
+      <c r="X28" s="209"/>
+      <c r="Y28" s="209"/>
+      <c r="Z28" s="209"/>
+      <c r="AA28" s="209"/>
+      <c r="AB28" s="209"/>
+      <c r="AC28" s="209"/>
     </row>
     <row r="29" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
       <c r="B29" s="114"/>
       <c r="C29" s="114"/>
       <c r="D29" s="114"/>
       <c r="E29" s="114"/>
-      <c r="F29" s="193" t="s">
-        <v>164</v>
+      <c r="F29" s="209" t="s">
+        <v>147</v>
       </c>
-      <c r="G29" s="193"/>
-      <c r="H29" s="193"/>
-      <c r="I29" s="193"/>
-      <c r="J29" s="193"/>
-      <c r="K29" s="193"/>
-      <c r="L29" s="193"/>
-      <c r="M29" s="193"/>
-      <c r="N29" s="193"/>
-      <c r="O29" s="193"/>
-      <c r="P29" s="193"/>
-      <c r="Q29" s="193"/>
-      <c r="R29" s="193"/>
-      <c r="S29" s="193"/>
-      <c r="T29" s="193"/>
-      <c r="U29" s="193"/>
-      <c r="V29" s="193"/>
-      <c r="W29" s="193"/>
-      <c r="X29" s="193"/>
-      <c r="Y29" s="193"/>
-      <c r="Z29" s="193"/>
-      <c r="AA29" s="193"/>
-      <c r="AB29" s="193"/>
-      <c r="AC29" s="193"/>
+      <c r="G29" s="209"/>
+      <c r="H29" s="209"/>
+      <c r="I29" s="209"/>
+      <c r="J29" s="209"/>
+      <c r="K29" s="209"/>
+      <c r="L29" s="209"/>
+      <c r="M29" s="209"/>
+      <c r="N29" s="209"/>
+      <c r="O29" s="209"/>
+      <c r="P29" s="209"/>
+      <c r="Q29" s="209"/>
+      <c r="R29" s="209"/>
+      <c r="S29" s="209"/>
+      <c r="T29" s="209"/>
+      <c r="U29" s="209"/>
+      <c r="V29" s="209"/>
+      <c r="W29" s="209"/>
+      <c r="X29" s="209"/>
+      <c r="Y29" s="209"/>
+      <c r="Z29" s="209"/>
+      <c r="AA29" s="209"/>
+      <c r="AB29" s="209"/>
+      <c r="AC29" s="209"/>
     </row>
     <row r="30" spans="2:29" s="37" customFormat="1" ht="10" customHeight="1">
       <c r="B30" s="114"/>
@@ -15933,39 +15988,39 @@
       <c r="AC30" s="116"/>
     </row>
     <row r="31" spans="2:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B31" s="192" t="s">
-        <v>141</v>
+      <c r="B31" s="207" t="s">
+        <v>161</v>
       </c>
-      <c r="C31" s="192"/>
-      <c r="D31" s="192"/>
-      <c r="E31" s="192"/>
-      <c r="F31" s="192"/>
-      <c r="G31" s="192"/>
-      <c r="H31" s="192"/>
-      <c r="I31" s="192"/>
-      <c r="J31" s="192"/>
-      <c r="K31" s="192"/>
-      <c r="L31" s="194" t="str">
+      <c r="C31" s="207"/>
+      <c r="D31" s="207"/>
+      <c r="E31" s="207"/>
+      <c r="F31" s="207"/>
+      <c r="G31" s="207"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="207"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="207"/>
+      <c r="L31" s="210" t="str">
         <f>대가산출!D3</f>
-        <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
+        <v>일금일백팔십만원정 (₩1,800,000) - VAT별도</v>
       </c>
-      <c r="M31" s="194"/>
-      <c r="N31" s="194"/>
-      <c r="O31" s="194"/>
-      <c r="P31" s="194"/>
-      <c r="Q31" s="194"/>
-      <c r="R31" s="194"/>
-      <c r="S31" s="194"/>
-      <c r="T31" s="194"/>
-      <c r="U31" s="194"/>
-      <c r="V31" s="194"/>
-      <c r="W31" s="194"/>
-      <c r="X31" s="194"/>
-      <c r="Y31" s="194"/>
-      <c r="Z31" s="194"/>
-      <c r="AA31" s="194"/>
-      <c r="AB31" s="194"/>
-      <c r="AC31" s="194"/>
+      <c r="M31" s="210"/>
+      <c r="N31" s="210"/>
+      <c r="O31" s="210"/>
+      <c r="P31" s="210"/>
+      <c r="Q31" s="210"/>
+      <c r="R31" s="210"/>
+      <c r="S31" s="210"/>
+      <c r="T31" s="210"/>
+      <c r="U31" s="210"/>
+      <c r="V31" s="210"/>
+      <c r="W31" s="210"/>
+      <c r="X31" s="210"/>
+      <c r="Y31" s="210"/>
+      <c r="Z31" s="210"/>
+      <c r="AA31" s="210"/>
+      <c r="AB31" s="210"/>
+      <c r="AC31" s="210"/>
     </row>
     <row r="32" spans="2:29" s="37" customFormat="1" ht="10" customHeight="1">
       <c r="B32" s="114"/>
@@ -15998,18 +16053,18 @@
       <c r="AC32" s="116"/>
     </row>
     <row r="33" spans="1:29" s="37" customFormat="1" ht="20" customHeight="1">
-      <c r="B33" s="190" t="s">
-        <v>140</v>
+      <c r="B33" s="208" t="s">
+        <v>160</v>
       </c>
-      <c r="C33" s="190"/>
-      <c r="D33" s="190"/>
-      <c r="E33" s="190"/>
-      <c r="F33" s="190"/>
-      <c r="G33" s="190"/>
-      <c r="H33" s="190"/>
-      <c r="I33" s="190"/>
-      <c r="J33" s="190"/>
-      <c r="K33" s="190"/>
+      <c r="C33" s="208"/>
+      <c r="D33" s="208"/>
+      <c r="E33" s="208"/>
+      <c r="F33" s="208"/>
+      <c r="G33" s="208"/>
+      <c r="H33" s="208"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="208"/>
       <c r="L33" s="38"/>
       <c r="M33" s="38"/>
       <c r="N33" s="38"/>
@@ -16090,36 +16145,36 @@
       <c r="AC35" s="43"/>
     </row>
     <row r="36" spans="1:29" s="37" customFormat="1" ht="19.5" customHeight="1">
-      <c r="B36" s="190" t="s">
-        <v>150</v>
+      <c r="B36" s="208" t="s">
+        <v>136</v>
       </c>
-      <c r="C36" s="190"/>
-      <c r="D36" s="190"/>
-      <c r="E36" s="190"/>
-      <c r="F36" s="190"/>
-      <c r="G36" s="190"/>
-      <c r="H36" s="190"/>
-      <c r="I36" s="190"/>
-      <c r="J36" s="190"/>
-      <c r="K36" s="190"/>
-      <c r="L36" s="190"/>
-      <c r="M36" s="190"/>
-      <c r="N36" s="190"/>
-      <c r="O36" s="190"/>
-      <c r="P36" s="190"/>
-      <c r="Q36" s="190"/>
-      <c r="R36" s="190"/>
-      <c r="S36" s="190"/>
-      <c r="T36" s="190"/>
-      <c r="U36" s="190"/>
-      <c r="V36" s="190"/>
-      <c r="W36" s="190"/>
-      <c r="X36" s="190"/>
-      <c r="Y36" s="190"/>
-      <c r="Z36" s="190"/>
-      <c r="AA36" s="190"/>
-      <c r="AB36" s="190"/>
-      <c r="AC36" s="190"/>
+      <c r="C36" s="208"/>
+      <c r="D36" s="208"/>
+      <c r="E36" s="208"/>
+      <c r="F36" s="208"/>
+      <c r="G36" s="208"/>
+      <c r="H36" s="208"/>
+      <c r="I36" s="208"/>
+      <c r="J36" s="208"/>
+      <c r="K36" s="208"/>
+      <c r="L36" s="208"/>
+      <c r="M36" s="208"/>
+      <c r="N36" s="208"/>
+      <c r="O36" s="208"/>
+      <c r="P36" s="208"/>
+      <c r="Q36" s="208"/>
+      <c r="R36" s="208"/>
+      <c r="S36" s="208"/>
+      <c r="T36" s="208"/>
+      <c r="U36" s="208"/>
+      <c r="V36" s="208"/>
+      <c r="W36" s="208"/>
+      <c r="X36" s="208"/>
+      <c r="Y36" s="208"/>
+      <c r="Z36" s="208"/>
+      <c r="AA36" s="208"/>
+      <c r="AB36" s="208"/>
+      <c r="AC36" s="208"/>
     </row>
     <row r="37" spans="1:29" s="37" customFormat="1" ht="19.5" customHeight="1">
       <c r="B37" s="38"/>
@@ -16137,36 +16192,36 @@
       <c r="N37" s="38"/>
     </row>
     <row r="38" spans="1:29" s="37" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B38" s="191" t="s">
-        <v>56</v>
+      <c r="B38" s="206" t="s">
+        <v>52</v>
       </c>
-      <c r="C38" s="191"/>
-      <c r="D38" s="191"/>
-      <c r="E38" s="191"/>
-      <c r="F38" s="191"/>
-      <c r="G38" s="191"/>
-      <c r="H38" s="191"/>
-      <c r="I38" s="191"/>
-      <c r="J38" s="191"/>
-      <c r="K38" s="191"/>
-      <c r="L38" s="191"/>
-      <c r="M38" s="191"/>
-      <c r="N38" s="191"/>
-      <c r="O38" s="191"/>
-      <c r="P38" s="191"/>
-      <c r="Q38" s="191"/>
-      <c r="R38" s="191"/>
-      <c r="S38" s="191"/>
-      <c r="T38" s="191"/>
-      <c r="U38" s="191"/>
-      <c r="V38" s="191"/>
-      <c r="W38" s="191"/>
-      <c r="X38" s="191"/>
-      <c r="Y38" s="191"/>
-      <c r="Z38" s="191"/>
-      <c r="AA38" s="191"/>
-      <c r="AB38" s="191"/>
-      <c r="AC38" s="191"/>
+      <c r="C38" s="206"/>
+      <c r="D38" s="206"/>
+      <c r="E38" s="206"/>
+      <c r="F38" s="206"/>
+      <c r="G38" s="206"/>
+      <c r="H38" s="206"/>
+      <c r="I38" s="206"/>
+      <c r="J38" s="206"/>
+      <c r="K38" s="206"/>
+      <c r="L38" s="206"/>
+      <c r="M38" s="206"/>
+      <c r="N38" s="206"/>
+      <c r="O38" s="206"/>
+      <c r="P38" s="206"/>
+      <c r="Q38" s="206"/>
+      <c r="R38" s="206"/>
+      <c r="S38" s="206"/>
+      <c r="T38" s="206"/>
+      <c r="U38" s="206"/>
+      <c r="V38" s="206"/>
+      <c r="W38" s="206"/>
+      <c r="X38" s="206"/>
+      <c r="Y38" s="206"/>
+      <c r="Z38" s="206"/>
+      <c r="AA38" s="206"/>
+      <c r="AB38" s="206"/>
+      <c r="AC38" s="206"/>
     </row>
     <row r="39" spans="1:29">
       <c r="A39" s="31"/>
@@ -33253,6 +33308,17 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B16:AC16"/>
+    <mergeCell ref="B18:AC18"/>
+    <mergeCell ref="B1:AC1"/>
+    <mergeCell ref="B3:AC3"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F7:R7"/>
+    <mergeCell ref="B14:AC14"/>
     <mergeCell ref="B38:AC38"/>
     <mergeCell ref="B31:K31"/>
     <mergeCell ref="B20:K20"/>
@@ -33267,17 +33333,6 @@
     <mergeCell ref="F28:AC28"/>
     <mergeCell ref="F29:AC29"/>
     <mergeCell ref="L31:AC31"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B16:AC16"/>
-    <mergeCell ref="B18:AC18"/>
-    <mergeCell ref="B1:AC1"/>
-    <mergeCell ref="B3:AC3"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F7:R7"/>
-    <mergeCell ref="B14:AC14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -33304,16 +33359,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" s="1" customFormat="1" ht="39" customHeight="1">
-      <c r="B1" s="173" t="s">
-        <v>120</v>
+      <c r="B1" s="216" t="s">
+        <v>111</v>
       </c>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
+      <c r="C1" s="216"/>
+      <c r="D1" s="216"/>
+      <c r="E1" s="216"/>
+      <c r="F1" s="216"/>
+      <c r="G1" s="216"/>
+      <c r="H1" s="216"/>
+      <c r="I1" s="216"/>
     </row>
     <row r="2" spans="2:9" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="B2" s="50"/>
@@ -33322,95 +33377,95 @@
       <c r="E2" s="50"/>
       <c r="F2" s="50"/>
       <c r="G2" s="50"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="217"/>
     </row>
     <row r="3" spans="2:9" s="51" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="B3" s="175" t="s">
-        <v>73</v>
+      <c r="B3" s="218" t="s">
+        <v>66</v>
       </c>
-      <c r="C3" s="176"/>
-      <c r="D3" s="177" t="str">
-        <f>"일금"&amp;NUMBERSTRING(H29,1)&amp;"원정 ("&amp;DOLLAR(H29,0)&amp;")-VAT별도"</f>
-        <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
+      <c r="C3" s="219"/>
+      <c r="D3" s="220" t="str">
+        <f>"일금"&amp;NUMBERSTRING(H29,1)&amp;"원정 ("&amp;DOLLAR(H29,0)&amp;") - VAT별도"</f>
+        <v>일금일백팔십만원정 (₩1,800,000) - VAT별도</v>
       </c>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="179"/>
+      <c r="E3" s="221"/>
+      <c r="F3" s="221"/>
+      <c r="G3" s="221"/>
+      <c r="H3" s="221"/>
+      <c r="I3" s="222"/>
     </row>
     <row r="4" spans="2:9" s="51" customFormat="1" ht="38.25" hidden="1" customHeight="1">
-      <c r="B4" s="180" t="s">
-        <v>74</v>
+      <c r="B4" s="223" t="s">
+        <v>67</v>
       </c>
-      <c r="C4" s="181"/>
-      <c r="D4" s="182" t="str">
+      <c r="C4" s="224"/>
+      <c r="D4" s="225" t="str">
         <f>"일금 "&amp;NUMBERSTRING(H29,1)&amp;"원정"&amp;TEXT(H29,"(￦ #,##0)")&amp;" "</f>
         <v xml:space="preserve">일금 일백팔십만원정(₩ 1,800,000) </v>
       </c>
-      <c r="E4" s="183"/>
-      <c r="F4" s="183"/>
-      <c r="G4" s="183"/>
-      <c r="H4" s="183"/>
-      <c r="I4" s="184"/>
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="226"/>
+      <c r="H4" s="226"/>
+      <c r="I4" s="227"/>
     </row>
     <row r="5" spans="2:9" s="51" customFormat="1" ht="38.25" hidden="1" customHeight="1" thickBot="1">
-      <c r="B5" s="155" t="s">
-        <v>75</v>
+      <c r="B5" s="233" t="s">
+        <v>68</v>
       </c>
-      <c r="C5" s="156"/>
-      <c r="D5" s="157" t="e">
+      <c r="C5" s="234"/>
+      <c r="D5" s="235" t="e">
         <f>"일금 "&amp;NUMBERSTRING(H30,1)&amp;"원정"&amp;TEXT(H30,"(￦ #,##0)")&amp;" "</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="159"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="237"/>
     </row>
     <row r="6" spans="2:9" s="51" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
-      <c r="B6" s="160" t="s">
-        <v>76</v>
+      <c r="B6" s="238" t="s">
+        <v>69</v>
       </c>
-      <c r="C6" s="161"/>
-      <c r="D6" s="161"/>
-      <c r="E6" s="161"/>
-      <c r="F6" s="161"/>
-      <c r="G6" s="161"/>
-      <c r="H6" s="161"/>
-      <c r="I6" s="162"/>
+      <c r="C6" s="239"/>
+      <c r="D6" s="239"/>
+      <c r="E6" s="239"/>
+      <c r="F6" s="239"/>
+      <c r="G6" s="239"/>
+      <c r="H6" s="239"/>
+      <c r="I6" s="240"/>
     </row>
     <row r="7" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="B7" s="163" t="s">
-        <v>77</v>
+      <c r="B7" s="241" t="s">
+        <v>70</v>
       </c>
-      <c r="C7" s="164"/>
+      <c r="C7" s="242"/>
       <c r="D7" s="49" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="2:9" s="52" customFormat="1" ht="28" customHeight="1">
-      <c r="B8" s="165" t="s">
-        <v>162</v>
+      <c r="B8" s="243" t="s">
+        <v>145</v>
       </c>
-      <c r="C8" s="166"/>
+      <c r="C8" s="244"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -33420,19 +33475,19 @@
         <v>1328145</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="2:9" s="52" customFormat="1" ht="18" customHeight="1">
       <c r="B9" s="54"/>
       <c r="C9" s="55" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E9" s="56" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F9" s="56">
         <v>0</v>
@@ -33450,10 +33505,10 @@
       <c r="B10" s="58"/>
       <c r="C10" s="59"/>
       <c r="D10" s="60" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E10" s="60" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F10" s="61">
         <v>1</v>
@@ -33471,10 +33526,10 @@
       <c r="B11" s="58"/>
       <c r="C11" s="59"/>
       <c r="D11" s="60" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E11" s="60" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F11" s="61">
         <v>0</v>
@@ -33492,10 +33547,10 @@
       <c r="B12" s="58"/>
       <c r="C12" s="59"/>
       <c r="D12" s="60" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E12" s="60" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F12" s="61">
         <v>1</v>
@@ -33512,13 +33567,13 @@
     <row r="13" spans="2:9" s="52" customFormat="1" ht="18" customHeight="1">
       <c r="B13" s="62"/>
       <c r="C13" s="63" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D13" s="60" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E13" s="60" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F13" s="61">
         <v>0</v>
@@ -33536,10 +33591,10 @@
       <c r="B14" s="58"/>
       <c r="C14" s="59"/>
       <c r="D14" s="60" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E14" s="60" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F14" s="61">
         <v>1</v>
@@ -33557,10 +33612,10 @@
       <c r="B15" s="58"/>
       <c r="C15" s="59"/>
       <c r="D15" s="60" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E15" s="60" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F15" s="61">
         <v>0</v>
@@ -33578,10 +33633,10 @@
       <c r="B16" s="58"/>
       <c r="C16" s="59"/>
       <c r="D16" s="60" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F16" s="61">
         <v>2</v>
@@ -33596,13 +33651,13 @@
       <c r="I16" s="57"/>
     </row>
     <row r="17" spans="2:13" s="52" customFormat="1" ht="28" customHeight="1">
-      <c r="B17" s="167" t="s">
-        <v>89</v>
+      <c r="B17" s="245" t="s">
+        <v>82</v>
       </c>
-      <c r="C17" s="168"/>
+      <c r="C17" s="246"/>
       <c r="D17" s="64"/>
       <c r="E17" s="66" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F17" s="66">
         <v>10</v>
@@ -33613,17 +33668,17 @@
         <v>132815</v>
       </c>
       <c r="I17" s="67" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="2:13" s="52" customFormat="1" ht="28" customHeight="1">
-      <c r="B18" s="167" t="s">
-        <v>91</v>
+      <c r="B18" s="245" t="s">
+        <v>84</v>
       </c>
-      <c r="C18" s="168"/>
+      <c r="C18" s="246"/>
       <c r="D18" s="64"/>
       <c r="E18" s="66" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F18" s="66">
         <v>10</v>
@@ -33634,14 +33689,14 @@
         <v>146096</v>
       </c>
       <c r="I18" s="67" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="2:13" s="52" customFormat="1" ht="28" customHeight="1">
-      <c r="B19" s="167" t="s">
-        <v>92</v>
+      <c r="B19" s="245" t="s">
+        <v>85</v>
       </c>
-      <c r="C19" s="168"/>
+      <c r="C19" s="246"/>
       <c r="D19" s="68"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
@@ -33654,7 +33709,7 @@
     </row>
     <row r="20" spans="2:13" s="52" customFormat="1" ht="18" customHeight="1">
       <c r="B20" s="71" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C20" s="72"/>
       <c r="D20" s="72"/>
@@ -33666,7 +33721,7 @@
     </row>
     <row r="21" spans="2:13" s="52" customFormat="1" ht="18" customHeight="1">
       <c r="B21" s="76" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C21" s="77"/>
       <c r="D21" s="77"/>
@@ -33688,7 +33743,7 @@
     </row>
     <row r="22" spans="2:13" s="52" customFormat="1" ht="18" customHeight="1">
       <c r="B22" s="81" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C22" s="82"/>
       <c r="D22" s="82"/>
@@ -33709,12 +33764,12 @@
     </row>
     <row r="23" spans="2:13" s="52" customFormat="1" ht="18" customHeight="1">
       <c r="B23" s="81" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C23" s="60"/>
       <c r="D23" s="82"/>
       <c r="E23" s="60" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F23" s="85">
         <v>10</v>
@@ -33725,17 +33780,17 @@
         <v>54634</v>
       </c>
       <c r="I23" s="79" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="2:13" s="52" customFormat="1" ht="18" customHeight="1">
       <c r="B24" s="81" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C24" s="60"/>
       <c r="D24" s="82"/>
       <c r="E24" s="60" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F24" s="86">
         <v>5</v>
@@ -33746,17 +33801,17 @@
         <v>66407</v>
       </c>
       <c r="I24" s="79" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="2:13" s="52" customFormat="1" ht="18" customHeight="1">
       <c r="B25" s="87" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C25" s="88"/>
       <c r="D25" s="89"/>
       <c r="E25" s="61" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F25" s="91">
         <v>1</v>
@@ -33771,10 +33826,10 @@
       <c r="I25" s="57"/>
     </row>
     <row r="26" spans="2:13" s="52" customFormat="1" ht="28" customHeight="1">
-      <c r="B26" s="169" t="s">
-        <v>101</v>
+      <c r="B26" s="247" t="s">
+        <v>94</v>
       </c>
-      <c r="C26" s="170"/>
+      <c r="C26" s="248"/>
       <c r="D26" s="64"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66"/>
@@ -33784,19 +33839,19 @@
         <v>0</v>
       </c>
       <c r="I26" s="95" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="2:13" s="52" customFormat="1" ht="28" customHeight="1">
-      <c r="B27" s="171" t="s">
-        <v>163</v>
+      <c r="B27" s="249" t="s">
+        <v>146</v>
       </c>
-      <c r="C27" s="172"/>
-      <c r="D27" s="147" t="s">
-        <v>103</v>
+      <c r="C27" s="250"/>
+      <c r="D27" s="230" t="s">
+        <v>96</v>
       </c>
-      <c r="E27" s="148"/>
-      <c r="F27" s="149"/>
+      <c r="E27" s="231"/>
+      <c r="F27" s="232"/>
       <c r="G27" s="111"/>
       <c r="H27" s="96">
         <f>H8+H17+H18+H19</f>
@@ -33805,13 +33860,13 @@
       <c r="I27" s="97"/>
     </row>
     <row r="28" spans="2:13" s="52" customFormat="1" ht="18" customHeight="1">
-      <c r="B28" s="145" t="s">
-        <v>104</v>
+      <c r="B28" s="228" t="s">
+        <v>97</v>
       </c>
-      <c r="C28" s="146"/>
-      <c r="D28" s="147"/>
-      <c r="E28" s="148"/>
-      <c r="F28" s="149"/>
+      <c r="C28" s="229"/>
+      <c r="D28" s="230"/>
+      <c r="E28" s="231"/>
+      <c r="F28" s="232"/>
       <c r="G28" s="111"/>
       <c r="H28" s="96">
         <v>38097</v>
@@ -33819,13 +33874,13 @@
       <c r="I28" s="98"/>
     </row>
     <row r="29" spans="2:13" s="52" customFormat="1" ht="18" customHeight="1">
-      <c r="B29" s="140" t="s">
-        <v>105</v>
+      <c r="B29" s="251" t="s">
+        <v>98</v>
       </c>
-      <c r="C29" s="141"/>
-      <c r="D29" s="142"/>
-      <c r="E29" s="143"/>
-      <c r="F29" s="144"/>
+      <c r="C29" s="252"/>
+      <c r="D29" s="253"/>
+      <c r="E29" s="254"/>
+      <c r="F29" s="255"/>
       <c r="G29" s="112"/>
       <c r="H29" s="99">
         <f>H27-H28</f>
@@ -33834,112 +33889,118 @@
       <c r="I29" s="100"/>
     </row>
     <row r="30" spans="2:13" s="52" customFormat="1" ht="18" customHeight="1">
-      <c r="B30" s="145" t="s">
-        <v>106</v>
+      <c r="B30" s="228" t="s">
+        <v>99</v>
       </c>
-      <c r="C30" s="146"/>
-      <c r="D30" s="147"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="149"/>
+      <c r="C30" s="229"/>
+      <c r="D30" s="230"/>
+      <c r="E30" s="231"/>
+      <c r="F30" s="232"/>
       <c r="G30" s="111"/>
       <c r="H30" s="101" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I30" s="98"/>
     </row>
     <row r="31" spans="2:13" s="52" customFormat="1" ht="28" customHeight="1" thickBot="1">
-      <c r="B31" s="150" t="s">
-        <v>108</v>
+      <c r="B31" s="256" t="s">
+        <v>101</v>
       </c>
-      <c r="C31" s="151"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="154"/>
+      <c r="C31" s="257"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="259"/>
+      <c r="F31" s="260"/>
       <c r="G31" s="113"/>
       <c r="H31" s="102">
         <f>H29</f>
         <v>1800000</v>
       </c>
       <c r="I31" s="103" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="2:13" s="105" customFormat="1" ht="23" customHeight="1">
-      <c r="B32" s="130"/>
-      <c r="C32" s="131"/>
-      <c r="D32" s="136" t="s">
+      <c r="B32" s="261"/>
+      <c r="C32" s="262"/>
+      <c r="D32" s="267" t="s">
         <v>1</v>
       </c>
-      <c r="E32" s="136"/>
-      <c r="F32" s="136"/>
-      <c r="G32" s="136"/>
-      <c r="H32" s="136"/>
+      <c r="E32" s="267"/>
+      <c r="F32" s="267"/>
+      <c r="G32" s="267"/>
+      <c r="H32" s="267"/>
       <c r="I32" s="104"/>
     </row>
     <row r="33" spans="2:9" s="105" customFormat="1" ht="23" customHeight="1">
-      <c r="B33" s="132"/>
-      <c r="C33" s="133"/>
-      <c r="D33" s="137" t="s">
+      <c r="B33" s="263"/>
+      <c r="C33" s="264"/>
+      <c r="D33" s="268" t="s">
         <v>2</v>
       </c>
-      <c r="E33" s="137"/>
-      <c r="F33" s="137"/>
-      <c r="G33" s="137"/>
-      <c r="H33" s="137"/>
+      <c r="E33" s="268"/>
+      <c r="F33" s="268"/>
+      <c r="G33" s="268"/>
+      <c r="H33" s="268"/>
       <c r="I33" s="106" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="2:9" s="105" customFormat="1" ht="23" customHeight="1">
-      <c r="B34" s="132"/>
-      <c r="C34" s="133"/>
-      <c r="D34" s="138" t="s">
+      <c r="B34" s="263"/>
+      <c r="C34" s="264"/>
+      <c r="D34" s="269" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="138"/>
-      <c r="F34" s="138"/>
-      <c r="G34" s="138"/>
-      <c r="H34" s="138"/>
+      <c r="E34" s="269"/>
+      <c r="F34" s="269"/>
+      <c r="G34" s="269"/>
+      <c r="H34" s="269"/>
       <c r="I34" s="106" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="2:9" s="105" customFormat="1" ht="23" customHeight="1">
-      <c r="B35" s="132"/>
-      <c r="C35" s="133"/>
-      <c r="D35" s="137" t="s">
+      <c r="B35" s="263"/>
+      <c r="C35" s="264"/>
+      <c r="D35" s="268" t="s">
         <v>6</v>
       </c>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="137"/>
-      <c r="H35" s="137"/>
+      <c r="E35" s="268"/>
+      <c r="F35" s="268"/>
+      <c r="G35" s="268"/>
+      <c r="H35" s="268"/>
       <c r="I35" s="106" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="2:9" s="105" customFormat="1" ht="23" customHeight="1" thickBot="1">
-      <c r="B36" s="134"/>
-      <c r="C36" s="135"/>
-      <c r="D36" s="139" t="s">
+      <c r="B36" s="265"/>
+      <c r="C36" s="266"/>
+      <c r="D36" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="139"/>
-      <c r="F36" s="139"/>
-      <c r="G36" s="139"/>
-      <c r="H36" s="139"/>
+      <c r="E36" s="270"/>
+      <c r="F36" s="270"/>
+      <c r="G36" s="270"/>
+      <c r="H36" s="270"/>
       <c r="I36" s="107" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="B32:C36"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="B5:C5"/>
@@ -33953,18 +34014,12 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="B32:C36"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -34460,99 +34515,99 @@
       <c r="C6" s="16"/>
     </row>
     <row r="7" spans="2:21" ht="4" customHeight="1">
-      <c r="B7" s="256" t="s">
+      <c r="B7" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="257"/>
-      <c r="D7" s="257"/>
-      <c r="E7" s="257"/>
-      <c r="F7" s="257"/>
-      <c r="G7" s="257"/>
-      <c r="H7" s="257"/>
-      <c r="I7" s="257"/>
-      <c r="J7" s="257"/>
-      <c r="K7" s="257"/>
-      <c r="L7" s="257"/>
-      <c r="M7" s="257"/>
-      <c r="N7" s="257"/>
-      <c r="O7" s="257"/>
-      <c r="P7" s="257"/>
-      <c r="Q7" s="257"/>
-      <c r="R7" s="257"/>
-      <c r="S7" s="257"/>
-      <c r="T7" s="257"/>
-      <c r="U7" s="257"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="127"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="127"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="127"/>
+      <c r="S7" s="127"/>
+      <c r="T7" s="127"/>
+      <c r="U7" s="127"/>
     </row>
     <row r="8" spans="2:21" ht="66" customHeight="1">
-      <c r="B8" s="258" t="s">
-        <v>110</v>
+      <c r="B8" s="128" t="s">
+        <v>103</v>
       </c>
-      <c r="C8" s="258"/>
-      <c r="D8" s="258"/>
-      <c r="E8" s="258"/>
-      <c r="F8" s="258"/>
-      <c r="G8" s="258"/>
-      <c r="H8" s="258"/>
-      <c r="I8" s="258"/>
-      <c r="J8" s="258"/>
-      <c r="K8" s="258"/>
-      <c r="L8" s="258"/>
-      <c r="M8" s="258"/>
-      <c r="N8" s="258"/>
-      <c r="O8" s="258"/>
-      <c r="P8" s="258"/>
-      <c r="Q8" s="258"/>
-      <c r="R8" s="258"/>
-      <c r="S8" s="258"/>
-      <c r="T8" s="258"/>
-      <c r="U8" s="258"/>
+      <c r="C8" s="128"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
+      <c r="L8" s="128"/>
+      <c r="M8" s="128"/>
+      <c r="N8" s="128"/>
+      <c r="O8" s="128"/>
+      <c r="P8" s="128"/>
+      <c r="Q8" s="128"/>
+      <c r="R8" s="128"/>
+      <c r="S8" s="128"/>
+      <c r="T8" s="128"/>
+      <c r="U8" s="128"/>
     </row>
     <row r="9" spans="2:21" ht="44" customHeight="1">
-      <c r="B9" s="259" t="str">
-        <f>갑지!F8</f>
+      <c r="B9" s="129" t="str">
+        <f>갑지!L21</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="C9" s="259"/>
-      <c r="D9" s="259"/>
-      <c r="E9" s="259"/>
-      <c r="F9" s="259"/>
-      <c r="G9" s="259"/>
-      <c r="H9" s="259"/>
-      <c r="I9" s="259"/>
-      <c r="J9" s="259"/>
-      <c r="K9" s="259"/>
-      <c r="L9" s="259"/>
-      <c r="M9" s="259"/>
-      <c r="N9" s="259"/>
-      <c r="O9" s="259"/>
-      <c r="P9" s="259"/>
-      <c r="Q9" s="259"/>
-      <c r="R9" s="259"/>
-      <c r="S9" s="259"/>
-      <c r="T9" s="259"/>
-      <c r="U9" s="259"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="129"/>
+      <c r="K9" s="129"/>
+      <c r="L9" s="129"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="129"/>
+      <c r="O9" s="129"/>
+      <c r="P9" s="129"/>
+      <c r="Q9" s="129"/>
+      <c r="R9" s="129"/>
+      <c r="S9" s="129"/>
+      <c r="T9" s="129"/>
+      <c r="U9" s="129"/>
     </row>
     <row r="10" spans="2:21" ht="4" customHeight="1">
-      <c r="B10" s="260"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
-      <c r="G10" s="261"/>
-      <c r="H10" s="261"/>
-      <c r="I10" s="261"/>
-      <c r="J10" s="261"/>
-      <c r="K10" s="261"/>
-      <c r="L10" s="261"/>
-      <c r="M10" s="261"/>
-      <c r="N10" s="261"/>
-      <c r="O10" s="261"/>
-      <c r="P10" s="261"/>
-      <c r="Q10" s="261"/>
-      <c r="R10" s="261"/>
-      <c r="S10" s="261"/>
-      <c r="T10" s="261"/>
-      <c r="U10" s="261"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="131"/>
+      <c r="T10" s="131"/>
+      <c r="U10" s="131"/>
     </row>
     <row r="11" spans="2:21" ht="50" customHeight="1">
       <c r="B11" s="18"/>
@@ -34575,29 +34630,29 @@
       <c r="C15" s="18"/>
     </row>
     <row r="16" spans="2:21" ht="24">
-      <c r="B16" s="262">
+      <c r="B16" s="132">
         <f>갑지!F7</f>
         <v>46072</v>
       </c>
-      <c r="C16" s="262"/>
-      <c r="D16" s="262"/>
-      <c r="E16" s="262"/>
-      <c r="F16" s="262"/>
-      <c r="G16" s="262"/>
-      <c r="H16" s="262"/>
-      <c r="I16" s="262"/>
-      <c r="J16" s="262"/>
-      <c r="K16" s="262"/>
-      <c r="L16" s="262"/>
-      <c r="M16" s="262"/>
-      <c r="N16" s="262"/>
-      <c r="O16" s="262"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="262"/>
-      <c r="R16" s="262"/>
-      <c r="S16" s="262"/>
-      <c r="T16" s="262"/>
-      <c r="U16" s="262"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="132"/>
+      <c r="K16" s="132"/>
+      <c r="L16" s="132"/>
+      <c r="M16" s="132"/>
+      <c r="N16" s="132"/>
+      <c r="O16" s="132"/>
+      <c r="P16" s="132"/>
+      <c r="Q16" s="132"/>
+      <c r="R16" s="132"/>
+      <c r="S16" s="132"/>
+      <c r="T16" s="132"/>
+      <c r="U16" s="132"/>
     </row>
     <row r="17" spans="2:21" ht="34.5" customHeight="1">
       <c r="B17" s="18"/>
@@ -34620,45 +34675,45 @@
       <c r="C21" s="18"/>
     </row>
     <row r="22" spans="2:21" ht="4" customHeight="1">
-      <c r="B22" s="267" t="s">
+      <c r="B22" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="268"/>
-      <c r="D22" s="268"/>
-      <c r="E22" s="268"/>
-      <c r="F22" s="268"/>
-      <c r="G22" s="268"/>
-      <c r="H22" s="268"/>
-      <c r="I22" s="268"/>
-      <c r="J22" s="268"/>
-      <c r="K22" s="268"/>
-      <c r="L22" s="268"/>
-      <c r="M22" s="268"/>
-      <c r="N22" s="268"/>
-      <c r="O22" s="268"/>
-      <c r="P22" s="268"/>
-      <c r="Q22" s="268"/>
-      <c r="R22" s="268"/>
-      <c r="S22" s="268"/>
-      <c r="T22" s="268"/>
-      <c r="U22" s="268"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="137"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="137"/>
+      <c r="O22" s="137"/>
+      <c r="P22" s="137"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="137"/>
+      <c r="S22" s="137"/>
+      <c r="T22" s="137"/>
+      <c r="U22" s="137"/>
     </row>
     <row r="23" spans="2:21" ht="53.25" customHeight="1">
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
-      <c r="I23" s="266" t="s">
+      <c r="I23" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="266"/>
-      <c r="K23" s="266"/>
-      <c r="L23" s="266"/>
-      <c r="M23" s="266"/>
-      <c r="N23" s="266"/>
-      <c r="O23" s="266"/>
-      <c r="P23" s="266"/>
-      <c r="Q23" s="266"/>
-      <c r="R23" s="266"/>
-      <c r="S23" s="266"/>
+      <c r="J23" s="136"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+      <c r="N23" s="136"/>
+      <c r="O23" s="136"/>
+      <c r="P23" s="136"/>
+      <c r="Q23" s="136"/>
+      <c r="R23" s="136"/>
+      <c r="S23" s="136"/>
       <c r="T23" s="48"/>
       <c r="U23" s="48"/>
     </row>
@@ -34666,40 +34721,40 @@
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
-      <c r="I24" s="221" t="s">
+      <c r="I24" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="J24" s="221"/>
-      <c r="K24" s="221"/>
-      <c r="L24" s="221"/>
-      <c r="M24" s="221"/>
-      <c r="N24" s="221"/>
-      <c r="O24" s="221"/>
-      <c r="P24" s="221"/>
-      <c r="Q24" s="221"/>
-      <c r="R24" s="221"/>
-      <c r="S24" s="221"/>
-      <c r="T24" s="221"/>
+      <c r="J24" s="138"/>
+      <c r="K24" s="138"/>
+      <c r="L24" s="138"/>
+      <c r="M24" s="138"/>
+      <c r="N24" s="138"/>
+      <c r="O24" s="138"/>
+      <c r="P24" s="138"/>
+      <c r="Q24" s="138"/>
+      <c r="R24" s="138"/>
+      <c r="S24" s="138"/>
+      <c r="T24" s="138"/>
       <c r="U24" s="19"/>
     </row>
     <row r="25" spans="2:21" ht="24" customHeight="1">
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
-      <c r="I25" s="221" t="s">
-        <v>72</v>
+      <c r="I25" s="138" t="s">
+        <v>65</v>
       </c>
-      <c r="J25" s="221"/>
-      <c r="K25" s="221"/>
-      <c r="L25" s="221"/>
-      <c r="M25" s="221"/>
-      <c r="N25" s="221"/>
-      <c r="O25" s="221"/>
-      <c r="P25" s="221"/>
-      <c r="Q25" s="221"/>
-      <c r="R25" s="221"/>
-      <c r="S25" s="221"/>
-      <c r="T25" s="221"/>
+      <c r="J25" s="138"/>
+      <c r="K25" s="138"/>
+      <c r="L25" s="138"/>
+      <c r="M25" s="138"/>
+      <c r="N25" s="138"/>
+      <c r="O25" s="138"/>
+      <c r="P25" s="138"/>
+      <c r="Q25" s="138"/>
+      <c r="R25" s="138"/>
+      <c r="S25" s="138"/>
+      <c r="T25" s="138"/>
       <c r="U25" s="19"/>
     </row>
     <row r="26" spans="2:21" ht="24" customHeight="1">
@@ -34737,454 +34792,452 @@
       <c r="U27" s="21"/>
     </row>
     <row r="28" spans="2:21" ht="43.5" customHeight="1" thickBot="1">
-      <c r="B28" s="263" t="s">
-        <v>111</v>
+      <c r="B28" s="133" t="s">
+        <v>104</v>
       </c>
-      <c r="C28" s="264"/>
-      <c r="D28" s="264"/>
-      <c r="E28" s="264"/>
-      <c r="F28" s="264"/>
-      <c r="G28" s="264"/>
-      <c r="H28" s="264"/>
-      <c r="I28" s="264"/>
-      <c r="J28" s="264"/>
-      <c r="K28" s="264"/>
-      <c r="L28" s="264"/>
-      <c r="M28" s="264"/>
-      <c r="N28" s="264"/>
-      <c r="O28" s="264"/>
-      <c r="P28" s="264"/>
-      <c r="Q28" s="264"/>
-      <c r="R28" s="264"/>
-      <c r="S28" s="264"/>
-      <c r="T28" s="264"/>
-      <c r="U28" s="265"/>
+      <c r="C28" s="134"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="134"/>
+      <c r="F28" s="134"/>
+      <c r="G28" s="134"/>
+      <c r="H28" s="134"/>
+      <c r="I28" s="134"/>
+      <c r="J28" s="134"/>
+      <c r="K28" s="134"/>
+      <c r="L28" s="134"/>
+      <c r="M28" s="134"/>
+      <c r="N28" s="134"/>
+      <c r="O28" s="134"/>
+      <c r="P28" s="134"/>
+      <c r="Q28" s="134"/>
+      <c r="R28" s="134"/>
+      <c r="S28" s="134"/>
+      <c r="T28" s="134"/>
+      <c r="U28" s="135"/>
     </row>
     <row r="29" spans="2:21" ht="25" customHeight="1">
-      <c r="B29" s="269" t="s">
+      <c r="B29" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="270"/>
-      <c r="D29" s="271" t="s">
+      <c r="C29" s="140"/>
+      <c r="D29" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="271"/>
-      <c r="F29" s="271"/>
-      <c r="G29" s="272" t="str">
+      <c r="E29" s="143"/>
+      <c r="F29" s="143"/>
+      <c r="G29" s="144" t="str">
         <f>B9</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="H29" s="272"/>
-      <c r="I29" s="272"/>
-      <c r="J29" s="272"/>
-      <c r="K29" s="272"/>
-      <c r="L29" s="272"/>
-      <c r="M29" s="272"/>
-      <c r="N29" s="272"/>
-      <c r="O29" s="272"/>
-      <c r="P29" s="272"/>
-      <c r="Q29" s="272"/>
-      <c r="R29" s="272"/>
-      <c r="S29" s="272"/>
-      <c r="T29" s="272"/>
-      <c r="U29" s="273"/>
+      <c r="H29" s="144"/>
+      <c r="I29" s="144"/>
+      <c r="J29" s="144"/>
+      <c r="K29" s="144"/>
+      <c r="L29" s="144"/>
+      <c r="M29" s="144"/>
+      <c r="N29" s="144"/>
+      <c r="O29" s="144"/>
+      <c r="P29" s="144"/>
+      <c r="Q29" s="144"/>
+      <c r="R29" s="144"/>
+      <c r="S29" s="144"/>
+      <c r="T29" s="144"/>
+      <c r="U29" s="145"/>
     </row>
     <row r="30" spans="2:21" ht="25" customHeight="1">
-      <c r="B30" s="232"/>
-      <c r="C30" s="233"/>
-      <c r="D30" s="231" t="s">
+      <c r="B30" s="141"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="146" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="231"/>
-      <c r="F30" s="231"/>
-      <c r="G30" s="246" t="s">
-        <v>151</v>
+      <c r="E30" s="146"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="147" t="s">
+        <v>137</v>
       </c>
-      <c r="H30" s="246"/>
-      <c r="I30" s="246"/>
-      <c r="J30" s="246"/>
-      <c r="K30" s="246"/>
-      <c r="L30" s="246"/>
-      <c r="M30" s="246"/>
-      <c r="N30" s="246"/>
-      <c r="O30" s="246"/>
-      <c r="P30" s="246"/>
-      <c r="Q30" s="246"/>
-      <c r="R30" s="246"/>
-      <c r="S30" s="246"/>
-      <c r="T30" s="246"/>
-      <c r="U30" s="247"/>
+      <c r="H30" s="147"/>
+      <c r="I30" s="147"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="147"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="147"/>
+      <c r="N30" s="147"/>
+      <c r="O30" s="147"/>
+      <c r="P30" s="147"/>
+      <c r="Q30" s="147"/>
+      <c r="R30" s="147"/>
+      <c r="S30" s="147"/>
+      <c r="T30" s="147"/>
+      <c r="U30" s="148"/>
     </row>
     <row r="31" spans="2:21" ht="25" customHeight="1">
-      <c r="B31" s="232"/>
-      <c r="C31" s="233"/>
-      <c r="D31" s="231"/>
-      <c r="E31" s="231"/>
-      <c r="F31" s="231"/>
-      <c r="G31" s="246" t="s">
-        <v>152</v>
+      <c r="B31" s="141"/>
+      <c r="C31" s="142"/>
+      <c r="D31" s="146"/>
+      <c r="E31" s="146"/>
+      <c r="F31" s="146"/>
+      <c r="G31" s="147" t="s">
+        <v>138</v>
       </c>
-      <c r="H31" s="246"/>
-      <c r="I31" s="246"/>
-      <c r="J31" s="246"/>
-      <c r="K31" s="246"/>
-      <c r="L31" s="246"/>
-      <c r="M31" s="246"/>
-      <c r="N31" s="246"/>
-      <c r="O31" s="246"/>
-      <c r="P31" s="246"/>
-      <c r="Q31" s="246"/>
-      <c r="R31" s="246"/>
-      <c r="S31" s="246"/>
-      <c r="T31" s="246"/>
-      <c r="U31" s="247"/>
+      <c r="H31" s="147"/>
+      <c r="I31" s="147"/>
+      <c r="J31" s="147"/>
+      <c r="K31" s="147"/>
+      <c r="L31" s="147"/>
+      <c r="M31" s="147"/>
+      <c r="N31" s="147"/>
+      <c r="O31" s="147"/>
+      <c r="P31" s="147"/>
+      <c r="Q31" s="147"/>
+      <c r="R31" s="147"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="147"/>
+      <c r="U31" s="148"/>
     </row>
     <row r="32" spans="2:21" ht="25" customHeight="1">
-      <c r="B32" s="232"/>
-      <c r="C32" s="233"/>
-      <c r="D32" s="231"/>
-      <c r="E32" s="231"/>
-      <c r="F32" s="231"/>
-      <c r="G32" s="246" t="s">
-        <v>155</v>
+      <c r="B32" s="141"/>
+      <c r="C32" s="142"/>
+      <c r="D32" s="146"/>
+      <c r="E32" s="146"/>
+      <c r="F32" s="146"/>
+      <c r="G32" s="147" t="s">
+        <v>141</v>
       </c>
-      <c r="H32" s="246"/>
-      <c r="I32" s="246"/>
-      <c r="J32" s="246"/>
-      <c r="K32" s="246"/>
-      <c r="L32" s="246"/>
-      <c r="M32" s="246"/>
-      <c r="N32" s="246"/>
-      <c r="O32" s="246"/>
-      <c r="P32" s="246"/>
-      <c r="Q32" s="246"/>
-      <c r="R32" s="246"/>
-      <c r="S32" s="246"/>
-      <c r="T32" s="246"/>
-      <c r="U32" s="247"/>
+      <c r="H32" s="147"/>
+      <c r="I32" s="147"/>
+      <c r="J32" s="147"/>
+      <c r="K32" s="147"/>
+      <c r="L32" s="147"/>
+      <c r="M32" s="147"/>
+      <c r="N32" s="147"/>
+      <c r="O32" s="147"/>
+      <c r="P32" s="147"/>
+      <c r="Q32" s="147"/>
+      <c r="R32" s="147"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="147"/>
+      <c r="U32" s="148"/>
     </row>
     <row r="33" spans="2:21" ht="25" customHeight="1">
-      <c r="B33" s="232"/>
-      <c r="C33" s="233"/>
-      <c r="D33" s="231"/>
-      <c r="E33" s="231"/>
-      <c r="F33" s="231"/>
-      <c r="G33" s="246" t="s">
-        <v>153</v>
+      <c r="B33" s="141"/>
+      <c r="C33" s="142"/>
+      <c r="D33" s="146"/>
+      <c r="E33" s="146"/>
+      <c r="F33" s="146"/>
+      <c r="G33" s="147" t="s">
+        <v>139</v>
       </c>
-      <c r="H33" s="246"/>
-      <c r="I33" s="246"/>
-      <c r="J33" s="246"/>
-      <c r="K33" s="246"/>
-      <c r="L33" s="246"/>
-      <c r="M33" s="246"/>
-      <c r="N33" s="246"/>
-      <c r="O33" s="246"/>
-      <c r="P33" s="246"/>
-      <c r="Q33" s="246"/>
-      <c r="R33" s="246"/>
-      <c r="S33" s="246"/>
-      <c r="T33" s="246"/>
-      <c r="U33" s="247"/>
+      <c r="H33" s="147"/>
+      <c r="I33" s="147"/>
+      <c r="J33" s="147"/>
+      <c r="K33" s="147"/>
+      <c r="L33" s="147"/>
+      <c r="M33" s="147"/>
+      <c r="N33" s="147"/>
+      <c r="O33" s="147"/>
+      <c r="P33" s="147"/>
+      <c r="Q33" s="147"/>
+      <c r="R33" s="147"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="147"/>
+      <c r="U33" s="148"/>
     </row>
     <row r="34" spans="2:21" ht="25" customHeight="1">
-      <c r="B34" s="232"/>
-      <c r="C34" s="233"/>
-      <c r="D34" s="231"/>
-      <c r="E34" s="231"/>
-      <c r="F34" s="231"/>
-      <c r="G34" s="248" t="s">
-        <v>154</v>
+      <c r="B34" s="141"/>
+      <c r="C34" s="142"/>
+      <c r="D34" s="146"/>
+      <c r="E34" s="146"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="149" t="s">
+        <v>140</v>
       </c>
-      <c r="H34" s="248"/>
-      <c r="I34" s="248"/>
-      <c r="J34" s="248"/>
-      <c r="K34" s="248"/>
-      <c r="L34" s="248"/>
-      <c r="M34" s="248"/>
-      <c r="N34" s="248"/>
-      <c r="O34" s="248"/>
-      <c r="P34" s="248"/>
-      <c r="Q34" s="248"/>
-      <c r="R34" s="248"/>
-      <c r="S34" s="248"/>
-      <c r="T34" s="248"/>
-      <c r="U34" s="249"/>
+      <c r="H34" s="149"/>
+      <c r="I34" s="149"/>
+      <c r="J34" s="149"/>
+      <c r="K34" s="149"/>
+      <c r="L34" s="149"/>
+      <c r="M34" s="149"/>
+      <c r="N34" s="149"/>
+      <c r="O34" s="149"/>
+      <c r="P34" s="149"/>
+      <c r="Q34" s="149"/>
+      <c r="R34" s="149"/>
+      <c r="S34" s="149"/>
+      <c r="T34" s="149"/>
+      <c r="U34" s="150"/>
     </row>
     <row r="35" spans="2:21" ht="25" customHeight="1">
-      <c r="B35" s="232" t="s">
+      <c r="B35" s="141" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="233"/>
-      <c r="D35" s="231" t="s">
+      <c r="C35" s="142"/>
+      <c r="D35" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="231"/>
-      <c r="F35" s="231"/>
-      <c r="G35" s="253" t="str">
-        <f>G29</f>
-        <v>효성뉴서울5차아파트</v>
+      <c r="E35" s="146"/>
+      <c r="F35" s="146"/>
+      <c r="G35" s="157" t="str">
+        <f>G29&amp;" 하자점검(조사) 용역"</f>
+        <v>효성뉴서울5차아파트 하자점검(조사) 용역</v>
       </c>
-      <c r="H35" s="254"/>
-      <c r="I35" s="254"/>
-      <c r="J35" s="254"/>
-      <c r="K35" s="254"/>
-      <c r="L35" s="254"/>
-      <c r="M35" s="254" t="s">
-        <v>112</v>
-      </c>
-      <c r="N35" s="254"/>
-      <c r="O35" s="254"/>
-      <c r="P35" s="254"/>
-      <c r="Q35" s="254"/>
-      <c r="R35" s="254"/>
-      <c r="S35" s="254"/>
-      <c r="T35" s="122"/>
-      <c r="U35" s="123"/>
+      <c r="H35" s="158"/>
+      <c r="I35" s="158"/>
+      <c r="J35" s="158"/>
+      <c r="K35" s="158"/>
+      <c r="L35" s="158"/>
+      <c r="M35" s="158"/>
+      <c r="N35" s="158"/>
+      <c r="O35" s="158"/>
+      <c r="P35" s="158"/>
+      <c r="Q35" s="158"/>
+      <c r="R35" s="158"/>
+      <c r="S35" s="158"/>
+      <c r="T35" s="158"/>
+      <c r="U35" s="159"/>
     </row>
     <row r="36" spans="2:21" ht="25" customHeight="1">
-      <c r="B36" s="232"/>
-      <c r="C36" s="233"/>
-      <c r="D36" s="231" t="s">
+      <c r="B36" s="141"/>
+      <c r="C36" s="142"/>
+      <c r="D36" s="146" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="231"/>
-      <c r="F36" s="231"/>
-      <c r="G36" s="229" t="str">
+      <c r="E36" s="146"/>
+      <c r="F36" s="146"/>
+      <c r="G36" s="168" t="str">
         <f>갑지!L31</f>
-        <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
+        <v>일금일백팔십만원정 (₩1,800,000) - VAT별도</v>
       </c>
-      <c r="H36" s="229"/>
-      <c r="I36" s="229"/>
-      <c r="J36" s="229"/>
-      <c r="K36" s="229"/>
-      <c r="L36" s="229"/>
-      <c r="M36" s="229"/>
-      <c r="N36" s="229"/>
-      <c r="O36" s="229"/>
-      <c r="P36" s="229"/>
-      <c r="Q36" s="229"/>
-      <c r="R36" s="229"/>
-      <c r="S36" s="229"/>
-      <c r="T36" s="229"/>
-      <c r="U36" s="230"/>
+      <c r="H36" s="168"/>
+      <c r="I36" s="168"/>
+      <c r="J36" s="168"/>
+      <c r="K36" s="168"/>
+      <c r="L36" s="168"/>
+      <c r="M36" s="168"/>
+      <c r="N36" s="168"/>
+      <c r="O36" s="168"/>
+      <c r="P36" s="168"/>
+      <c r="Q36" s="168"/>
+      <c r="R36" s="168"/>
+      <c r="S36" s="168"/>
+      <c r="T36" s="168"/>
+      <c r="U36" s="169"/>
     </row>
     <row r="37" spans="2:21" ht="25" customHeight="1">
-      <c r="B37" s="232"/>
-      <c r="C37" s="233"/>
-      <c r="D37" s="231" t="s">
+      <c r="B37" s="141"/>
+      <c r="C37" s="142"/>
+      <c r="D37" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="E37" s="231"/>
-      <c r="F37" s="231"/>
-      <c r="G37" s="238" t="str">
+      <c r="E37" s="146"/>
+      <c r="F37" s="146"/>
+      <c r="G37" s="170" t="str">
         <f>갑지!L31</f>
-        <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
+        <v>일금일백팔십만원정 (₩1,800,000) - VAT별도</v>
       </c>
-      <c r="H37" s="238"/>
-      <c r="I37" s="238"/>
-      <c r="J37" s="238"/>
-      <c r="K37" s="238"/>
-      <c r="L37" s="238"/>
-      <c r="M37" s="238"/>
-      <c r="N37" s="238"/>
-      <c r="O37" s="238"/>
-      <c r="P37" s="238"/>
-      <c r="Q37" s="238"/>
-      <c r="R37" s="238"/>
-      <c r="S37" s="238"/>
-      <c r="T37" s="238"/>
-      <c r="U37" s="239"/>
+      <c r="H37" s="170"/>
+      <c r="I37" s="170"/>
+      <c r="J37" s="170"/>
+      <c r="K37" s="170"/>
+      <c r="L37" s="170"/>
+      <c r="M37" s="170"/>
+      <c r="N37" s="170"/>
+      <c r="O37" s="170"/>
+      <c r="P37" s="170"/>
+      <c r="Q37" s="170"/>
+      <c r="R37" s="170"/>
+      <c r="S37" s="170"/>
+      <c r="T37" s="170"/>
+      <c r="U37" s="171"/>
     </row>
     <row r="38" spans="2:21" ht="25" customHeight="1">
-      <c r="B38" s="232"/>
-      <c r="C38" s="233"/>
-      <c r="D38" s="231" t="s">
+      <c r="B38" s="141"/>
+      <c r="C38" s="142"/>
+      <c r="D38" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="231"/>
-      <c r="F38" s="231"/>
-      <c r="G38" s="229" t="s">
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="162" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="229"/>
-      <c r="I38" s="229"/>
-      <c r="J38" s="229"/>
-      <c r="K38" s="229"/>
-      <c r="L38" s="229"/>
-      <c r="M38" s="229"/>
-      <c r="N38" s="229"/>
-      <c r="O38" s="229"/>
-      <c r="P38" s="229"/>
-      <c r="Q38" s="229"/>
-      <c r="R38" s="229"/>
-      <c r="S38" s="229"/>
-      <c r="T38" s="229"/>
-      <c r="U38" s="230"/>
+      <c r="H38" s="162"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="162"/>
+      <c r="K38" s="162"/>
+      <c r="L38" s="162"/>
+      <c r="M38" s="162"/>
+      <c r="N38" s="162"/>
+      <c r="O38" s="162"/>
+      <c r="P38" s="162"/>
+      <c r="Q38" s="162"/>
+      <c r="R38" s="162"/>
+      <c r="S38" s="162"/>
+      <c r="T38" s="162"/>
+      <c r="U38" s="163"/>
     </row>
     <row r="39" spans="2:21" ht="25" customHeight="1">
-      <c r="B39" s="232"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="231" t="s">
+      <c r="B39" s="141"/>
+      <c r="C39" s="142"/>
+      <c r="D39" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="231"/>
-      <c r="F39" s="231"/>
-      <c r="G39" s="229" t="s">
-        <v>55</v>
+      <c r="E39" s="146"/>
+      <c r="F39" s="146"/>
+      <c r="G39" s="162" t="s">
+        <v>51</v>
       </c>
-      <c r="H39" s="229"/>
-      <c r="I39" s="229"/>
-      <c r="J39" s="229"/>
-      <c r="K39" s="229"/>
-      <c r="L39" s="229"/>
-      <c r="M39" s="229"/>
-      <c r="N39" s="229"/>
-      <c r="O39" s="229"/>
-      <c r="P39" s="229"/>
-      <c r="Q39" s="229"/>
-      <c r="R39" s="229"/>
-      <c r="S39" s="229"/>
-      <c r="T39" s="229"/>
-      <c r="U39" s="230"/>
+      <c r="H39" s="162"/>
+      <c r="I39" s="162"/>
+      <c r="J39" s="162"/>
+      <c r="K39" s="162"/>
+      <c r="L39" s="162"/>
+      <c r="M39" s="162"/>
+      <c r="N39" s="162"/>
+      <c r="O39" s="162"/>
+      <c r="P39" s="162"/>
+      <c r="Q39" s="162"/>
+      <c r="R39" s="162"/>
+      <c r="S39" s="162"/>
+      <c r="T39" s="162"/>
+      <c r="U39" s="163"/>
     </row>
     <row r="40" spans="2:21" ht="25" customHeight="1">
-      <c r="B40" s="232"/>
-      <c r="C40" s="233"/>
-      <c r="D40" s="231" t="s">
+      <c r="B40" s="141"/>
+      <c r="C40" s="142"/>
+      <c r="D40" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="231"/>
-      <c r="F40" s="231"/>
-      <c r="G40" s="229" t="str">
+      <c r="E40" s="146"/>
+      <c r="F40" s="146"/>
+      <c r="G40" s="162" t="str">
         <f>갑지!L23</f>
         <v>인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="H40" s="229"/>
-      <c r="I40" s="229"/>
-      <c r="J40" s="229"/>
-      <c r="K40" s="229"/>
-      <c r="L40" s="229"/>
-      <c r="M40" s="229"/>
-      <c r="N40" s="229"/>
-      <c r="O40" s="229"/>
-      <c r="P40" s="229"/>
-      <c r="Q40" s="229"/>
-      <c r="R40" s="229"/>
-      <c r="S40" s="229"/>
-      <c r="T40" s="229"/>
-      <c r="U40" s="230"/>
+      <c r="H40" s="162"/>
+      <c r="I40" s="162"/>
+      <c r="J40" s="162"/>
+      <c r="K40" s="162"/>
+      <c r="L40" s="162"/>
+      <c r="M40" s="162"/>
+      <c r="N40" s="162"/>
+      <c r="O40" s="162"/>
+      <c r="P40" s="162"/>
+      <c r="Q40" s="162"/>
+      <c r="R40" s="162"/>
+      <c r="S40" s="162"/>
+      <c r="T40" s="162"/>
+      <c r="U40" s="163"/>
     </row>
     <row r="41" spans="2:21" ht="25" customHeight="1">
-      <c r="B41" s="232"/>
-      <c r="C41" s="233"/>
-      <c r="D41" s="231"/>
-      <c r="E41" s="231"/>
-      <c r="F41" s="231"/>
-      <c r="G41" s="253" t="s">
-        <v>142</v>
+      <c r="B41" s="141"/>
+      <c r="C41" s="142"/>
+      <c r="D41" s="146"/>
+      <c r="E41" s="146"/>
+      <c r="F41" s="146"/>
+      <c r="G41" s="154" t="s">
+        <v>129</v>
       </c>
-      <c r="H41" s="254"/>
-      <c r="I41" s="254"/>
-      <c r="J41" s="254"/>
-      <c r="K41" s="254"/>
-      <c r="L41" s="254"/>
-      <c r="M41" s="254"/>
-      <c r="N41" s="121" t="s">
-        <v>143</v>
+      <c r="H41" s="155"/>
+      <c r="I41" s="155"/>
+      <c r="J41" s="155"/>
+      <c r="K41" s="155"/>
+      <c r="L41" s="155"/>
+      <c r="M41" s="155"/>
+      <c r="N41" s="124" t="s">
+        <v>130</v>
       </c>
-      <c r="O41" s="254" t="s">
-        <v>144</v>
+      <c r="O41" s="155" t="s">
+        <v>131</v>
       </c>
-      <c r="P41" s="254"/>
-      <c r="Q41" s="254"/>
-      <c r="R41" s="254"/>
-      <c r="S41" s="254"/>
-      <c r="T41" s="254"/>
-      <c r="U41" s="255"/>
+      <c r="P41" s="155"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="155"/>
+      <c r="S41" s="155"/>
+      <c r="T41" s="155"/>
+      <c r="U41" s="156"/>
     </row>
     <row r="42" spans="2:21" ht="25" customHeight="1">
-      <c r="B42" s="234"/>
-      <c r="C42" s="235"/>
-      <c r="D42" s="240" t="s">
+      <c r="B42" s="164"/>
+      <c r="C42" s="165"/>
+      <c r="D42" s="172" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="241"/>
-      <c r="F42" s="242"/>
-      <c r="G42" s="243" t="s">
-        <v>113</v>
+      <c r="E42" s="173"/>
+      <c r="F42" s="174"/>
+      <c r="G42" s="175" t="s">
+        <v>105</v>
       </c>
-      <c r="H42" s="244"/>
-      <c r="I42" s="244"/>
-      <c r="J42" s="244"/>
-      <c r="K42" s="244"/>
-      <c r="L42" s="244"/>
-      <c r="M42" s="244"/>
-      <c r="N42" s="244"/>
-      <c r="O42" s="244"/>
-      <c r="P42" s="244"/>
-      <c r="Q42" s="244"/>
-      <c r="R42" s="244"/>
-      <c r="S42" s="244"/>
-      <c r="T42" s="244"/>
-      <c r="U42" s="245"/>
+      <c r="H42" s="176"/>
+      <c r="I42" s="176"/>
+      <c r="J42" s="176"/>
+      <c r="K42" s="176"/>
+      <c r="L42" s="176"/>
+      <c r="M42" s="176"/>
+      <c r="N42" s="176"/>
+      <c r="O42" s="176"/>
+      <c r="P42" s="176"/>
+      <c r="Q42" s="176"/>
+      <c r="R42" s="176"/>
+      <c r="S42" s="176"/>
+      <c r="T42" s="176"/>
+      <c r="U42" s="177"/>
     </row>
     <row r="43" spans="2:21" ht="25" customHeight="1" thickBot="1">
-      <c r="B43" s="236"/>
-      <c r="C43" s="237"/>
-      <c r="D43" s="250" t="s">
+      <c r="B43" s="166"/>
+      <c r="C43" s="167"/>
+      <c r="D43" s="151" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="250"/>
-      <c r="F43" s="250"/>
-      <c r="G43" s="251" t="s">
-        <v>114</v>
+      <c r="E43" s="151"/>
+      <c r="F43" s="151"/>
+      <c r="G43" s="152" t="s">
+        <v>106</v>
       </c>
-      <c r="H43" s="251"/>
-      <c r="I43" s="251"/>
-      <c r="J43" s="251"/>
-      <c r="K43" s="251"/>
-      <c r="L43" s="251"/>
-      <c r="M43" s="251"/>
-      <c r="N43" s="251"/>
-      <c r="O43" s="251"/>
-      <c r="P43" s="251"/>
-      <c r="Q43" s="251"/>
-      <c r="R43" s="251"/>
-      <c r="S43" s="251"/>
-      <c r="T43" s="251"/>
-      <c r="U43" s="252"/>
+      <c r="H43" s="152"/>
+      <c r="I43" s="152"/>
+      <c r="J43" s="152"/>
+      <c r="K43" s="152"/>
+      <c r="L43" s="152"/>
+      <c r="M43" s="152"/>
+      <c r="N43" s="152"/>
+      <c r="O43" s="152"/>
+      <c r="P43" s="152"/>
+      <c r="Q43" s="152"/>
+      <c r="R43" s="152"/>
+      <c r="S43" s="152"/>
+      <c r="T43" s="152"/>
+      <c r="U43" s="153"/>
     </row>
     <row r="44" spans="2:21">
-      <c r="B44" s="223"/>
-      <c r="C44" s="224"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="224"/>
+      <c r="B44" s="178"/>
+      <c r="C44" s="179"/>
+      <c r="D44" s="179"/>
+      <c r="E44" s="179"/>
       <c r="U44" s="2"/>
     </row>
     <row r="45" spans="2:21" ht="67.5" customHeight="1">
-      <c r="B45" s="225" t="s">
+      <c r="B45" s="160" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="196"/>
-      <c r="D45" s="196"/>
-      <c r="E45" s="196"/>
-      <c r="F45" s="196"/>
-      <c r="G45" s="196"/>
-      <c r="H45" s="196"/>
-      <c r="I45" s="196"/>
-      <c r="J45" s="196"/>
-      <c r="K45" s="196"/>
-      <c r="L45" s="196"/>
-      <c r="M45" s="196"/>
-      <c r="N45" s="196"/>
-      <c r="O45" s="196"/>
-      <c r="P45" s="196"/>
-      <c r="Q45" s="196"/>
-      <c r="R45" s="196"/>
-      <c r="S45" s="196"/>
-      <c r="T45" s="196"/>
-      <c r="U45" s="222"/>
+      <c r="C45" s="125"/>
+      <c r="D45" s="125"/>
+      <c r="E45" s="125"/>
+      <c r="F45" s="125"/>
+      <c r="G45" s="125"/>
+      <c r="H45" s="125"/>
+      <c r="I45" s="125"/>
+      <c r="J45" s="125"/>
+      <c r="K45" s="125"/>
+      <c r="L45" s="125"/>
+      <c r="M45" s="125"/>
+      <c r="N45" s="125"/>
+      <c r="O45" s="125"/>
+      <c r="P45" s="125"/>
+      <c r="Q45" s="125"/>
+      <c r="R45" s="125"/>
+      <c r="S45" s="125"/>
+      <c r="T45" s="125"/>
+      <c r="U45" s="161"/>
     </row>
     <row r="46" spans="2:21">
       <c r="B46" s="22"/>
@@ -35194,273 +35247,273 @@
       <c r="U46" s="2"/>
     </row>
     <row r="47" spans="2:21" ht="25" customHeight="1">
-      <c r="B47" s="220" t="s">
+      <c r="B47" s="185" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="221"/>
-      <c r="D47" s="221"/>
-      <c r="E47" s="196" t="s">
-        <v>115</v>
+      <c r="C47" s="138"/>
+      <c r="D47" s="138"/>
+      <c r="E47" s="125" t="s">
+        <v>107</v>
       </c>
-      <c r="F47" s="196"/>
-      <c r="G47" s="196"/>
-      <c r="H47" s="196"/>
-      <c r="I47" s="196"/>
-      <c r="J47" s="196"/>
-      <c r="K47" s="196"/>
-      <c r="L47" s="196"/>
-      <c r="M47" s="196"/>
-      <c r="N47" s="196"/>
-      <c r="O47" s="196"/>
-      <c r="P47" s="196"/>
-      <c r="Q47" s="196"/>
-      <c r="R47" s="196"/>
-      <c r="S47" s="196"/>
-      <c r="T47" s="196"/>
-      <c r="U47" s="222"/>
+      <c r="F47" s="125"/>
+      <c r="G47" s="125"/>
+      <c r="H47" s="125"/>
+      <c r="I47" s="125"/>
+      <c r="J47" s="125"/>
+      <c r="K47" s="125"/>
+      <c r="L47" s="125"/>
+      <c r="M47" s="125"/>
+      <c r="N47" s="125"/>
+      <c r="O47" s="125"/>
+      <c r="P47" s="125"/>
+      <c r="Q47" s="125"/>
+      <c r="R47" s="125"/>
+      <c r="S47" s="125"/>
+      <c r="T47" s="125"/>
+      <c r="U47" s="161"/>
     </row>
     <row r="48" spans="2:21" ht="25" customHeight="1">
       <c r="B48" s="24"/>
       <c r="C48" s="19"/>
       <c r="D48" s="19"/>
-      <c r="E48" s="196"/>
-      <c r="F48" s="196"/>
-      <c r="G48" s="196"/>
-      <c r="H48" s="196"/>
-      <c r="I48" s="196"/>
-      <c r="J48" s="196"/>
-      <c r="K48" s="196"/>
-      <c r="L48" s="196"/>
-      <c r="M48" s="196"/>
-      <c r="N48" s="196"/>
-      <c r="O48" s="196"/>
-      <c r="P48" s="196"/>
-      <c r="Q48" s="196"/>
-      <c r="R48" s="196"/>
-      <c r="S48" s="196"/>
-      <c r="T48" s="196"/>
-      <c r="U48" s="222"/>
+      <c r="E48" s="125"/>
+      <c r="F48" s="125"/>
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="125"/>
+      <c r="J48" s="125"/>
+      <c r="K48" s="125"/>
+      <c r="L48" s="125"/>
+      <c r="M48" s="125"/>
+      <c r="N48" s="125"/>
+      <c r="O48" s="125"/>
+      <c r="P48" s="125"/>
+      <c r="Q48" s="125"/>
+      <c r="R48" s="125"/>
+      <c r="S48" s="125"/>
+      <c r="T48" s="125"/>
+      <c r="U48" s="161"/>
     </row>
     <row r="49" spans="2:41" ht="25" customHeight="1">
       <c r="B49" s="24"/>
       <c r="C49" s="19"/>
       <c r="D49" s="19"/>
-      <c r="E49" s="196"/>
-      <c r="F49" s="196"/>
-      <c r="G49" s="196"/>
-      <c r="H49" s="196"/>
-      <c r="I49" s="196"/>
-      <c r="J49" s="196"/>
-      <c r="K49" s="196"/>
-      <c r="L49" s="196"/>
-      <c r="M49" s="196"/>
-      <c r="N49" s="196"/>
-      <c r="O49" s="196"/>
-      <c r="P49" s="196"/>
-      <c r="Q49" s="196"/>
-      <c r="R49" s="196"/>
-      <c r="S49" s="196"/>
-      <c r="T49" s="196"/>
-      <c r="U49" s="222"/>
+      <c r="E49" s="125"/>
+      <c r="F49" s="125"/>
+      <c r="G49" s="125"/>
+      <c r="H49" s="125"/>
+      <c r="I49" s="125"/>
+      <c r="J49" s="125"/>
+      <c r="K49" s="125"/>
+      <c r="L49" s="125"/>
+      <c r="M49" s="125"/>
+      <c r="N49" s="125"/>
+      <c r="O49" s="125"/>
+      <c r="P49" s="125"/>
+      <c r="Q49" s="125"/>
+      <c r="R49" s="125"/>
+      <c r="S49" s="125"/>
+      <c r="T49" s="125"/>
+      <c r="U49" s="161"/>
     </row>
     <row r="50" spans="2:41">
-      <c r="B50" s="223"/>
-      <c r="C50" s="224"/>
-      <c r="D50" s="224"/>
-      <c r="E50" s="224"/>
+      <c r="B50" s="178"/>
+      <c r="C50" s="179"/>
+      <c r="D50" s="179"/>
+      <c r="E50" s="179"/>
       <c r="U50" s="2"/>
     </row>
     <row r="51" spans="2:41" ht="25" customHeight="1">
-      <c r="B51" s="225" t="s">
+      <c r="B51" s="160" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="196"/>
-      <c r="D51" s="196"/>
-      <c r="E51" s="226" t="s">
-        <v>116</v>
+      <c r="C51" s="125"/>
+      <c r="D51" s="125"/>
+      <c r="E51" s="186" t="s">
+        <v>108</v>
       </c>
-      <c r="F51" s="226"/>
-      <c r="G51" s="226"/>
-      <c r="H51" s="226"/>
-      <c r="I51" s="226"/>
-      <c r="J51" s="226"/>
-      <c r="K51" s="226"/>
-      <c r="L51" s="226"/>
-      <c r="M51" s="226"/>
-      <c r="N51" s="226"/>
-      <c r="O51" s="226"/>
-      <c r="P51" s="226"/>
-      <c r="Q51" s="226"/>
-      <c r="R51" s="226"/>
-      <c r="S51" s="226"/>
-      <c r="T51" s="226"/>
-      <c r="U51" s="227"/>
+      <c r="F51" s="186"/>
+      <c r="G51" s="186"/>
+      <c r="H51" s="186"/>
+      <c r="I51" s="186"/>
+      <c r="J51" s="186"/>
+      <c r="K51" s="186"/>
+      <c r="L51" s="186"/>
+      <c r="M51" s="186"/>
+      <c r="N51" s="186"/>
+      <c r="O51" s="186"/>
+      <c r="P51" s="186"/>
+      <c r="Q51" s="186"/>
+      <c r="R51" s="186"/>
+      <c r="S51" s="186"/>
+      <c r="T51" s="186"/>
+      <c r="U51" s="187"/>
     </row>
     <row r="52" spans="2:41" ht="40.5" customHeight="1">
-      <c r="B52" s="207" t="s">
+      <c r="B52" s="180" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="208"/>
-      <c r="D52" s="208"/>
-      <c r="E52" s="208"/>
-      <c r="F52" s="208"/>
-      <c r="G52" s="208"/>
-      <c r="H52" s="208"/>
-      <c r="I52" s="208"/>
-      <c r="J52" s="208"/>
-      <c r="K52" s="208"/>
-      <c r="L52" s="208" t="s">
+      <c r="C52" s="181"/>
+      <c r="D52" s="181"/>
+      <c r="E52" s="181"/>
+      <c r="F52" s="181"/>
+      <c r="G52" s="181"/>
+      <c r="H52" s="181"/>
+      <c r="I52" s="181"/>
+      <c r="J52" s="181"/>
+      <c r="K52" s="181"/>
+      <c r="L52" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="M52" s="208"/>
-      <c r="N52" s="208"/>
-      <c r="O52" s="208"/>
-      <c r="P52" s="208"/>
-      <c r="Q52" s="208"/>
-      <c r="R52" s="208"/>
-      <c r="S52" s="208"/>
-      <c r="T52" s="208"/>
-      <c r="U52" s="228"/>
+      <c r="M52" s="181"/>
+      <c r="N52" s="181"/>
+      <c r="O52" s="181"/>
+      <c r="P52" s="181"/>
+      <c r="Q52" s="181"/>
+      <c r="R52" s="181"/>
+      <c r="S52" s="181"/>
+      <c r="T52" s="181"/>
+      <c r="U52" s="188"/>
     </row>
     <row r="53" spans="2:41" ht="40.5" customHeight="1">
-      <c r="B53" s="207" t="s">
+      <c r="B53" s="180" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="208"/>
-      <c r="D53" s="208"/>
-      <c r="E53" s="209" t="str">
+      <c r="C53" s="181"/>
+      <c r="D53" s="181"/>
+      <c r="E53" s="182" t="str">
         <f>G29</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="F53" s="209"/>
-      <c r="G53" s="209"/>
-      <c r="H53" s="209"/>
-      <c r="I53" s="209"/>
-      <c r="J53" s="209"/>
-      <c r="K53" s="209"/>
-      <c r="L53" s="208" t="s">
+      <c r="F53" s="182"/>
+      <c r="G53" s="182"/>
+      <c r="H53" s="182"/>
+      <c r="I53" s="182"/>
+      <c r="J53" s="182"/>
+      <c r="K53" s="182"/>
+      <c r="L53" s="181" t="s">
         <v>31</v>
       </c>
-      <c r="M53" s="208"/>
-      <c r="N53" s="208"/>
-      <c r="O53" s="218" t="s">
+      <c r="M53" s="181"/>
+      <c r="N53" s="181"/>
+      <c r="O53" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="P53" s="218"/>
-      <c r="Q53" s="218"/>
-      <c r="R53" s="218"/>
-      <c r="S53" s="218"/>
-      <c r="T53" s="218"/>
-      <c r="U53" s="219"/>
+      <c r="P53" s="183"/>
+      <c r="Q53" s="183"/>
+      <c r="R53" s="183"/>
+      <c r="S53" s="183"/>
+      <c r="T53" s="183"/>
+      <c r="U53" s="184"/>
     </row>
     <row r="54" spans="2:41" ht="40.5" customHeight="1">
-      <c r="B54" s="207" t="s">
+      <c r="B54" s="180" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="208"/>
-      <c r="D54" s="208"/>
-      <c r="E54" s="209" t="str">
+      <c r="C54" s="181"/>
+      <c r="D54" s="181"/>
+      <c r="E54" s="182" t="str">
         <f>G40</f>
         <v>인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="F54" s="209"/>
-      <c r="G54" s="209"/>
-      <c r="H54" s="209"/>
-      <c r="I54" s="209"/>
-      <c r="J54" s="209"/>
-      <c r="K54" s="209"/>
-      <c r="L54" s="208" t="s">
+      <c r="F54" s="182"/>
+      <c r="G54" s="182"/>
+      <c r="H54" s="182"/>
+      <c r="I54" s="182"/>
+      <c r="J54" s="182"/>
+      <c r="K54" s="182"/>
+      <c r="L54" s="181" t="s">
         <v>34</v>
       </c>
-      <c r="M54" s="208"/>
-      <c r="N54" s="208"/>
-      <c r="O54" s="210" t="s">
+      <c r="M54" s="181"/>
+      <c r="N54" s="181"/>
+      <c r="O54" s="189" t="s">
         <v>35</v>
       </c>
-      <c r="P54" s="211"/>
-      <c r="Q54" s="211"/>
-      <c r="R54" s="211"/>
-      <c r="S54" s="211"/>
-      <c r="T54" s="211"/>
-      <c r="U54" s="212"/>
+      <c r="P54" s="190"/>
+      <c r="Q54" s="190"/>
+      <c r="R54" s="190"/>
+      <c r="S54" s="190"/>
+      <c r="T54" s="190"/>
+      <c r="U54" s="191"/>
     </row>
     <row r="55" spans="2:41" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B55" s="213" t="s">
+      <c r="B55" s="192" t="s">
         <v>36</v>
       </c>
-      <c r="C55" s="214"/>
-      <c r="D55" s="214"/>
-      <c r="E55" s="215" t="s">
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
+      <c r="E55" s="194" t="s">
         <v>37</v>
       </c>
-      <c r="F55" s="215"/>
-      <c r="G55" s="215"/>
-      <c r="H55" s="215"/>
-      <c r="I55" s="215"/>
-      <c r="J55" s="215"/>
-      <c r="K55" s="215"/>
-      <c r="L55" s="214" t="s">
+      <c r="F55" s="194"/>
+      <c r="G55" s="194"/>
+      <c r="H55" s="194"/>
+      <c r="I55" s="194"/>
+      <c r="J55" s="194"/>
+      <c r="K55" s="194"/>
+      <c r="L55" s="193" t="s">
         <v>38</v>
       </c>
-      <c r="M55" s="214"/>
-      <c r="N55" s="214"/>
-      <c r="O55" s="216" t="s">
+      <c r="M55" s="193"/>
+      <c r="N55" s="193"/>
+      <c r="O55" s="195" t="s">
         <v>39</v>
       </c>
-      <c r="P55" s="216"/>
-      <c r="Q55" s="216"/>
-      <c r="R55" s="216"/>
-      <c r="S55" s="216"/>
-      <c r="T55" s="216"/>
-      <c r="U55" s="217"/>
+      <c r="P55" s="195"/>
+      <c r="Q55" s="195"/>
+      <c r="R55" s="195"/>
+      <c r="S55" s="195"/>
+      <c r="T55" s="195"/>
+      <c r="U55" s="196"/>
     </row>
     <row r="56" spans="2:41" ht="16">
-      <c r="B56" s="204" t="s">
+      <c r="B56" s="200" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="204"/>
-      <c r="D56" s="204"/>
-      <c r="E56" s="204"/>
-      <c r="F56" s="204"/>
-      <c r="G56" s="204"/>
-      <c r="H56" s="204"/>
-      <c r="I56" s="204"/>
-      <c r="J56" s="204"/>
-      <c r="K56" s="204"/>
-      <c r="L56" s="204"/>
-      <c r="M56" s="204"/>
-      <c r="N56" s="204"/>
-      <c r="O56" s="204"/>
-      <c r="P56" s="204"/>
-      <c r="Q56" s="204"/>
-      <c r="R56" s="204"/>
-      <c r="S56" s="204"/>
-      <c r="T56" s="204"/>
-      <c r="U56" s="204"/>
+      <c r="C56" s="200"/>
+      <c r="D56" s="200"/>
+      <c r="E56" s="200"/>
+      <c r="F56" s="200"/>
+      <c r="G56" s="200"/>
+      <c r="H56" s="200"/>
+      <c r="I56" s="200"/>
+      <c r="J56" s="200"/>
+      <c r="K56" s="200"/>
+      <c r="L56" s="200"/>
+      <c r="M56" s="200"/>
+      <c r="N56" s="200"/>
+      <c r="O56" s="200"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="200"/>
+      <c r="S56" s="200"/>
+      <c r="T56" s="200"/>
+      <c r="U56" s="200"/>
     </row>
     <row r="57" spans="2:41" ht="26">
-      <c r="B57" s="205" t="s">
-        <v>117</v>
+      <c r="B57" s="201" t="s">
+        <v>109</v>
       </c>
-      <c r="C57" s="205"/>
-      <c r="D57" s="205"/>
-      <c r="E57" s="205"/>
-      <c r="F57" s="205"/>
-      <c r="G57" s="205"/>
-      <c r="H57" s="205"/>
-      <c r="I57" s="205"/>
-      <c r="J57" s="205"/>
-      <c r="K57" s="205"/>
-      <c r="L57" s="205"/>
-      <c r="M57" s="205"/>
-      <c r="N57" s="205"/>
-      <c r="O57" s="205"/>
-      <c r="P57" s="205"/>
-      <c r="Q57" s="205"/>
-      <c r="R57" s="205"/>
-      <c r="S57" s="205"/>
-      <c r="T57" s="205"/>
-      <c r="U57" s="205"/>
+      <c r="C57" s="201"/>
+      <c r="D57" s="201"/>
+      <c r="E57" s="201"/>
+      <c r="F57" s="201"/>
+      <c r="G57" s="201"/>
+      <c r="H57" s="201"/>
+      <c r="I57" s="201"/>
+      <c r="J57" s="201"/>
+      <c r="K57" s="201"/>
+      <c r="L57" s="201"/>
+      <c r="M57" s="201"/>
+      <c r="N57" s="201"/>
+      <c r="O57" s="201"/>
+      <c r="P57" s="201"/>
+      <c r="Q57" s="201"/>
+      <c r="R57" s="201"/>
+      <c r="S57" s="201"/>
+      <c r="T57" s="201"/>
+      <c r="U57" s="201"/>
     </row>
     <row r="58" spans="2:41" ht="15">
       <c r="B58" s="25"/>
@@ -35469,79 +35522,74 @@
       <c r="I58" s="3"/>
     </row>
     <row r="59" spans="2:41" s="29" customFormat="1" ht="33" customHeight="1">
-      <c r="B59" s="206" t="s">
-        <v>156</v>
+      <c r="C59" s="203" t="s">
+        <v>164</v>
       </c>
-      <c r="C59" s="206"/>
-      <c r="D59" s="206"/>
-      <c r="E59" s="206"/>
-      <c r="F59" s="206"/>
-      <c r="G59" s="206"/>
-      <c r="H59" s="206"/>
-      <c r="I59" s="206"/>
-      <c r="J59" s="206"/>
-      <c r="K59" s="206"/>
-      <c r="L59" s="206"/>
-      <c r="M59" s="206"/>
-      <c r="N59" s="206"/>
-      <c r="O59" s="206"/>
-      <c r="P59" s="206"/>
-      <c r="Q59" s="206"/>
-      <c r="R59" s="206"/>
-      <c r="S59" s="206"/>
-      <c r="T59" s="206"/>
-      <c r="U59" s="206"/>
+      <c r="D59" s="203"/>
+      <c r="E59" s="203"/>
+      <c r="F59" s="203"/>
+      <c r="G59" s="203"/>
+      <c r="H59" s="203"/>
+      <c r="I59" s="203"/>
+      <c r="J59" s="203"/>
+      <c r="K59" s="203"/>
+      <c r="L59" s="203"/>
+      <c r="M59" s="203"/>
+      <c r="N59" s="203"/>
+      <c r="O59" s="203"/>
+      <c r="P59" s="203"/>
+      <c r="Q59" s="203"/>
+      <c r="R59" s="203"/>
+      <c r="S59" s="203"/>
+      <c r="T59" s="203"/>
+      <c r="U59" s="203"/>
     </row>
     <row r="60" spans="2:41" ht="20" customHeight="1">
-      <c r="B60" s="200" t="str">
-        <f>E53</f>
-        <v>효성뉴서울5차아파트</v>
+      <c r="C60" s="204" t="str">
+        <f>"규정에 따라 "&amp;E53&amp;"(이하 ""발주자""라 한다)와 하자점검(조사)의 실시자인"</f>
+        <v>규정에 따라 효성뉴서울5차아파트(이하 "발주자"라 한다)와 하자점검(조사)의 실시자인</v>
       </c>
-      <c r="C60" s="200"/>
-      <c r="D60" s="200"/>
-      <c r="E60" s="200"/>
-      <c r="F60" s="200"/>
-      <c r="G60" s="200"/>
-      <c r="H60" s="200"/>
-      <c r="I60" s="200"/>
-      <c r="J60" s="203" t="s">
-        <v>157</v>
+      <c r="D60" s="204"/>
+      <c r="E60" s="204"/>
+      <c r="F60" s="204"/>
+      <c r="G60" s="204"/>
+      <c r="H60" s="204"/>
+      <c r="I60" s="204"/>
+      <c r="J60" s="204"/>
+      <c r="K60" s="204"/>
+      <c r="L60" s="204"/>
+      <c r="M60" s="204"/>
+      <c r="N60" s="204"/>
+      <c r="O60" s="204"/>
+      <c r="P60" s="204"/>
+      <c r="Q60" s="204"/>
+      <c r="R60" s="204"/>
+      <c r="S60" s="204"/>
+      <c r="T60" s="204"/>
+      <c r="U60" s="204"/>
+    </row>
+    <row r="61" spans="2:41" ht="20" customHeight="1">
+      <c r="C61" s="205" t="s">
+        <v>165</v>
       </c>
-      <c r="K60" s="203"/>
-      <c r="L60" s="203"/>
-      <c r="M60" s="203"/>
-      <c r="N60" s="203"/>
-      <c r="O60" s="203"/>
-      <c r="P60" s="203"/>
-      <c r="Q60" s="203"/>
-      <c r="R60" s="203"/>
-      <c r="S60" s="203"/>
-      <c r="T60" s="203"/>
-      <c r="U60" s="203"/>
-    </row>
-    <row r="61" spans="2:41" ht="20" customHeight="1">
-      <c r="B61" s="201" t="s">
-        <v>145</v>
-      </c>
-      <c r="C61" s="201"/>
-      <c r="D61" s="201"/>
-      <c r="E61" s="201"/>
-      <c r="F61" s="201"/>
-      <c r="G61" s="201"/>
-      <c r="H61" s="201"/>
-      <c r="I61" s="201"/>
-      <c r="J61" s="201"/>
-      <c r="K61" s="201"/>
-      <c r="L61" s="201"/>
-      <c r="M61" s="201"/>
-      <c r="N61" s="201"/>
-      <c r="O61" s="201"/>
-      <c r="P61" s="201"/>
-      <c r="Q61" s="201"/>
-      <c r="R61" s="201"/>
-      <c r="S61" s="201"/>
-      <c r="T61" s="201"/>
-      <c r="U61" s="201"/>
+      <c r="D61" s="205"/>
+      <c r="E61" s="205"/>
+      <c r="F61" s="205"/>
+      <c r="G61" s="205"/>
+      <c r="H61" s="205"/>
+      <c r="I61" s="205"/>
+      <c r="J61" s="205"/>
+      <c r="K61" s="205"/>
+      <c r="L61" s="205"/>
+      <c r="M61" s="205"/>
+      <c r="N61" s="205"/>
+      <c r="O61" s="205"/>
+      <c r="P61" s="205"/>
+      <c r="Q61" s="205"/>
+      <c r="R61" s="205"/>
+      <c r="S61" s="205"/>
+      <c r="T61" s="205"/>
+      <c r="U61" s="205"/>
     </row>
     <row r="62" spans="2:41" ht="20" customHeight="1">
       <c r="B62" s="20"/>
@@ -35556,7 +35604,7 @@
     </row>
     <row r="63" spans="2:41" ht="20" customHeight="1">
       <c r="B63" s="197" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="C63" s="198"/>
       <c r="D63" s="198"/>
@@ -35568,46 +35616,46 @@
       <c r="J63" s="198"/>
     </row>
     <row r="64" spans="2:41" ht="63.75" customHeight="1">
-      <c r="C64" s="196" t="s">
-        <v>118</v>
+      <c r="C64" s="125" t="s">
+        <v>110</v>
       </c>
-      <c r="D64" s="196"/>
-      <c r="E64" s="196"/>
-      <c r="F64" s="196"/>
-      <c r="G64" s="196"/>
-      <c r="H64" s="196"/>
-      <c r="I64" s="196"/>
-      <c r="J64" s="196"/>
-      <c r="K64" s="196"/>
-      <c r="L64" s="196"/>
-      <c r="M64" s="196"/>
-      <c r="N64" s="196"/>
-      <c r="O64" s="196"/>
-      <c r="P64" s="196"/>
-      <c r="Q64" s="196"/>
-      <c r="R64" s="196"/>
-      <c r="S64" s="196"/>
-      <c r="T64" s="196"/>
-      <c r="U64" s="196"/>
-      <c r="W64" s="196"/>
-      <c r="X64" s="196"/>
-      <c r="Y64" s="196"/>
-      <c r="Z64" s="196"/>
-      <c r="AA64" s="196"/>
-      <c r="AB64" s="196"/>
-      <c r="AC64" s="196"/>
-      <c r="AD64" s="196"/>
-      <c r="AE64" s="196"/>
-      <c r="AF64" s="196"/>
-      <c r="AG64" s="196"/>
-      <c r="AH64" s="196"/>
-      <c r="AI64" s="196"/>
-      <c r="AJ64" s="196"/>
-      <c r="AK64" s="196"/>
-      <c r="AL64" s="196"/>
-      <c r="AM64" s="196"/>
-      <c r="AN64" s="196"/>
-      <c r="AO64" s="196"/>
+      <c r="D64" s="125"/>
+      <c r="E64" s="125"/>
+      <c r="F64" s="125"/>
+      <c r="G64" s="125"/>
+      <c r="H64" s="125"/>
+      <c r="I64" s="125"/>
+      <c r="J64" s="125"/>
+      <c r="K64" s="125"/>
+      <c r="L64" s="125"/>
+      <c r="M64" s="125"/>
+      <c r="N64" s="125"/>
+      <c r="O64" s="125"/>
+      <c r="P64" s="125"/>
+      <c r="Q64" s="125"/>
+      <c r="R64" s="125"/>
+      <c r="S64" s="125"/>
+      <c r="T64" s="125"/>
+      <c r="U64" s="125"/>
+      <c r="W64" s="125"/>
+      <c r="X64" s="125"/>
+      <c r="Y64" s="125"/>
+      <c r="Z64" s="125"/>
+      <c r="AA64" s="125"/>
+      <c r="AB64" s="125"/>
+      <c r="AC64" s="125"/>
+      <c r="AD64" s="125"/>
+      <c r="AE64" s="125"/>
+      <c r="AF64" s="125"/>
+      <c r="AG64" s="125"/>
+      <c r="AH64" s="125"/>
+      <c r="AI64" s="125"/>
+      <c r="AJ64" s="125"/>
+      <c r="AK64" s="125"/>
+      <c r="AL64" s="125"/>
+      <c r="AM64" s="125"/>
+      <c r="AN64" s="125"/>
+      <c r="AO64" s="125"/>
     </row>
     <row r="65" spans="2:21" ht="20" customHeight="1">
       <c r="B65" s="26"/>
@@ -35617,7 +35665,7 @@
     </row>
     <row r="66" spans="2:21" ht="20" customHeight="1">
       <c r="B66" s="197" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C66" s="197"/>
       <c r="D66" s="197"/>
@@ -35640,107 +35688,99 @@
       <c r="U66" s="197"/>
     </row>
     <row r="67" spans="2:21" ht="20" customHeight="1">
-      <c r="C67" s="27" t="s">
-        <v>41</v>
+      <c r="C67" s="199" t="str">
+        <f>"① 시설물명 : "&amp;E53</f>
+        <v>① 시설물명 : 효성뉴서울5차아파트</v>
       </c>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="202" t="str">
-        <f>E53</f>
-        <v>효성뉴서울5차아파트</v>
+      <c r="D67" s="199"/>
+      <c r="E67" s="199"/>
+      <c r="F67" s="199"/>
+      <c r="G67" s="199"/>
+      <c r="H67" s="199"/>
+      <c r="I67" s="199"/>
+      <c r="J67" s="199"/>
+      <c r="K67" s="199"/>
+      <c r="L67" s="199"/>
+      <c r="M67" s="199"/>
+      <c r="N67" s="199"/>
+      <c r="O67" s="199"/>
+      <c r="P67" s="199"/>
+      <c r="Q67" s="199"/>
+      <c r="R67" s="199"/>
+      <c r="S67" s="199"/>
+      <c r="T67" s="199"/>
+      <c r="U67" s="199"/>
+    </row>
+    <row r="68" spans="2:21" ht="20" customHeight="1">
+      <c r="C68" s="199" t="str">
+        <f>"② 위      치 : "&amp;E54</f>
+        <v>② 위      치 : 인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="G67" s="202"/>
-      <c r="H67" s="202"/>
-      <c r="I67" s="202"/>
-      <c r="J67" s="202"/>
-      <c r="K67" s="202"/>
-      <c r="L67" s="202"/>
-      <c r="M67" s="202"/>
-      <c r="N67" s="202"/>
-      <c r="O67" s="202"/>
-      <c r="P67" s="202"/>
-      <c r="Q67" s="202"/>
-      <c r="R67" s="202"/>
-      <c r="S67" s="202"/>
-      <c r="T67" s="202"/>
-      <c r="U67" s="202"/>
-    </row>
-    <row r="68" spans="2:21" ht="20" customHeight="1">
-      <c r="C68" s="27" t="s">
-        <v>42</v>
+      <c r="D68" s="199"/>
+      <c r="E68" s="199"/>
+      <c r="F68" s="199"/>
+      <c r="G68" s="199"/>
+      <c r="H68" s="199"/>
+      <c r="I68" s="199"/>
+      <c r="J68" s="199"/>
+      <c r="K68" s="199"/>
+      <c r="L68" s="199"/>
+      <c r="M68" s="199"/>
+      <c r="N68" s="199"/>
+      <c r="O68" s="199"/>
+      <c r="P68" s="199"/>
+      <c r="Q68" s="199"/>
+      <c r="R68" s="199"/>
+      <c r="S68" s="199"/>
+      <c r="T68" s="199"/>
+      <c r="U68" s="199"/>
+    </row>
+    <row r="69" spans="2:21" ht="20" customHeight="1">
+      <c r="C69" s="199" t="s">
+        <v>162</v>
       </c>
-      <c r="D68" s="27"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="124" t="str">
-        <f>E54</f>
-        <v>인천 계양구 아나지로 199 (효성동)</v>
-      </c>
-      <c r="G68" s="124"/>
-      <c r="H68" s="124"/>
-      <c r="I68" s="124"/>
-      <c r="J68" s="124"/>
-      <c r="K68" s="125"/>
-      <c r="L68" s="126"/>
-      <c r="M68" s="126"/>
-      <c r="N68" s="126"/>
-      <c r="O68" s="126"/>
-      <c r="P68" s="126"/>
-      <c r="Q68" s="126"/>
-      <c r="R68" s="126"/>
-      <c r="S68" s="126"/>
-      <c r="T68" s="126"/>
-      <c r="U68" s="126"/>
-    </row>
-    <row r="69" spans="2:21" ht="20" customHeight="1">
-      <c r="C69" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="124" t="s">
-        <v>50</v>
-      </c>
-      <c r="G69" s="124"/>
-      <c r="H69" s="124"/>
-      <c r="I69" s="124"/>
-      <c r="J69" s="124"/>
-      <c r="K69" s="127"/>
-      <c r="L69" s="128"/>
-      <c r="M69" s="128"/>
-      <c r="N69" s="128"/>
-      <c r="O69" s="128"/>
-      <c r="P69" s="128"/>
-      <c r="Q69" s="128"/>
-      <c r="R69" s="128"/>
-      <c r="S69" s="128"/>
-      <c r="T69" s="128"/>
-      <c r="U69" s="128"/>
+      <c r="D69" s="199"/>
+      <c r="E69" s="199"/>
+      <c r="F69" s="199"/>
+      <c r="G69" s="199"/>
+      <c r="H69" s="199"/>
+      <c r="I69" s="199"/>
+      <c r="J69" s="199"/>
+      <c r="K69" s="199"/>
+      <c r="L69" s="199"/>
+      <c r="M69" s="199"/>
+      <c r="N69" s="199"/>
+      <c r="O69" s="199"/>
+      <c r="P69" s="199"/>
+      <c r="Q69" s="199"/>
+      <c r="R69" s="199"/>
+      <c r="S69" s="199"/>
+      <c r="T69" s="199"/>
+      <c r="U69" s="199"/>
     </row>
     <row r="70" spans="2:21" ht="20" customHeight="1">
-      <c r="C70" s="27" t="s">
-        <v>119</v>
+      <c r="C70" s="27" t="str">
+        <f>"④ 하자점검(조사) 대상시설물의 범위 : "&amp;갑지!L22</f>
+        <v xml:space="preserve">④ 하자점검(조사) 대상시설물의 범위 : 아파트 6개동 648세대 (해당동 : 6개동) </v>
       </c>
       <c r="D70" s="27"/>
       <c r="E70" s="27"/>
-      <c r="F70" s="124"/>
-      <c r="G70" s="124"/>
-      <c r="H70" s="124"/>
-      <c r="I70" s="124"/>
-      <c r="J70" s="128"/>
-      <c r="K70" s="124" t="str">
-        <f>갑지!L22</f>
-        <v xml:space="preserve">아파트 6개동 648세대 (해당동 : 6개동) </v>
-      </c>
-      <c r="L70" s="129"/>
-      <c r="M70" s="129"/>
-      <c r="N70" s="129"/>
-      <c r="O70" s="129"/>
-      <c r="P70" s="129"/>
-      <c r="Q70" s="129"/>
-      <c r="R70" s="129"/>
-      <c r="S70" s="129"/>
-      <c r="T70" s="128"/>
-      <c r="U70" s="128"/>
+      <c r="F70" s="121"/>
+      <c r="G70" s="121"/>
+      <c r="H70" s="121"/>
+      <c r="I70" s="121"/>
+      <c r="J70" s="122"/>
+      <c r="K70" s="121"/>
+      <c r="L70" s="123"/>
+      <c r="M70" s="123"/>
+      <c r="N70" s="123"/>
+      <c r="O70" s="123"/>
+      <c r="P70" s="123"/>
+      <c r="Q70" s="123"/>
+      <c r="R70" s="123"/>
+      <c r="S70" s="123"/>
+      <c r="T70" s="122"/>
+      <c r="U70" s="122"/>
     </row>
     <row r="71" spans="2:21" ht="20" customHeight="1">
       <c r="B71" s="26"/>
@@ -35750,7 +35790,7 @@
     </row>
     <row r="72" spans="2:21" ht="17">
       <c r="B72" s="197" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C72" s="198"/>
       <c r="D72" s="198"/>
@@ -35763,7 +35803,7 @@
     </row>
     <row r="73" spans="2:21" ht="20" customHeight="1">
       <c r="C73" s="27" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="27"/>
@@ -35774,27 +35814,27 @@
       <c r="J73" s="27"/>
     </row>
     <row r="74" spans="2:21" ht="40" customHeight="1">
-      <c r="C74" s="196" t="s">
-        <v>136</v>
+      <c r="C74" s="125" t="s">
+        <v>127</v>
       </c>
-      <c r="D74" s="196"/>
-      <c r="E74" s="196"/>
-      <c r="F74" s="196"/>
-      <c r="G74" s="196"/>
-      <c r="H74" s="196"/>
-      <c r="I74" s="196"/>
-      <c r="J74" s="196"/>
-      <c r="K74" s="196"/>
-      <c r="L74" s="196"/>
-      <c r="M74" s="196"/>
-      <c r="N74" s="196"/>
-      <c r="O74" s="196"/>
-      <c r="P74" s="196"/>
-      <c r="Q74" s="196"/>
-      <c r="R74" s="196"/>
-      <c r="S74" s="196"/>
-      <c r="T74" s="196"/>
-      <c r="U74" s="196"/>
+      <c r="D74" s="125"/>
+      <c r="E74" s="125"/>
+      <c r="F74" s="125"/>
+      <c r="G74" s="125"/>
+      <c r="H74" s="125"/>
+      <c r="I74" s="125"/>
+      <c r="J74" s="125"/>
+      <c r="K74" s="125"/>
+      <c r="L74" s="125"/>
+      <c r="M74" s="125"/>
+      <c r="N74" s="125"/>
+      <c r="O74" s="125"/>
+      <c r="P74" s="125"/>
+      <c r="Q74" s="125"/>
+      <c r="R74" s="125"/>
+      <c r="S74" s="125"/>
+      <c r="T74" s="125"/>
+      <c r="U74" s="125"/>
     </row>
     <row r="75" spans="2:21" ht="20" customHeight="1">
       <c r="B75" s="26"/>
@@ -35804,7 +35844,7 @@
     </row>
     <row r="76" spans="2:21" ht="20" customHeight="1">
       <c r="B76" s="197" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C76" s="198"/>
       <c r="D76" s="198"/>
@@ -35816,27 +35856,27 @@
       <c r="J76" s="198"/>
     </row>
     <row r="77" spans="2:21" ht="42.75" customHeight="1">
-      <c r="C77" s="196" t="s">
-        <v>122</v>
+      <c r="C77" s="125" t="s">
+        <v>113</v>
       </c>
-      <c r="D77" s="196"/>
-      <c r="E77" s="196"/>
-      <c r="F77" s="196"/>
-      <c r="G77" s="196"/>
-      <c r="H77" s="196"/>
-      <c r="I77" s="196"/>
-      <c r="J77" s="196"/>
-      <c r="K77" s="196"/>
-      <c r="L77" s="196"/>
-      <c r="M77" s="196"/>
-      <c r="N77" s="196"/>
-      <c r="O77" s="196"/>
-      <c r="P77" s="196"/>
-      <c r="Q77" s="196"/>
-      <c r="R77" s="196"/>
-      <c r="S77" s="196"/>
-      <c r="T77" s="196"/>
-      <c r="U77" s="196"/>
+      <c r="D77" s="125"/>
+      <c r="E77" s="125"/>
+      <c r="F77" s="125"/>
+      <c r="G77" s="125"/>
+      <c r="H77" s="125"/>
+      <c r="I77" s="125"/>
+      <c r="J77" s="125"/>
+      <c r="K77" s="125"/>
+      <c r="L77" s="125"/>
+      <c r="M77" s="125"/>
+      <c r="N77" s="125"/>
+      <c r="O77" s="125"/>
+      <c r="P77" s="125"/>
+      <c r="Q77" s="125"/>
+      <c r="R77" s="125"/>
+      <c r="S77" s="125"/>
+      <c r="T77" s="125"/>
+      <c r="U77" s="125"/>
     </row>
     <row r="78" spans="2:21" ht="20" customHeight="1">
       <c r="C78" s="27"/>
@@ -35850,7 +35890,7 @@
     </row>
     <row r="79" spans="2:21" ht="20" customHeight="1">
       <c r="B79" s="197" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C79" s="198"/>
       <c r="D79" s="198"/>
@@ -35862,50 +35902,50 @@
       <c r="J79" s="198"/>
     </row>
     <row r="80" spans="2:21" ht="40" customHeight="1">
-      <c r="C80" s="196" t="s">
-        <v>45</v>
+      <c r="C80" s="125" t="s">
+        <v>42</v>
       </c>
-      <c r="D80" s="196"/>
-      <c r="E80" s="196"/>
-      <c r="F80" s="196"/>
-      <c r="G80" s="196"/>
-      <c r="H80" s="196"/>
-      <c r="I80" s="196"/>
-      <c r="J80" s="196"/>
-      <c r="K80" s="196"/>
-      <c r="L80" s="196"/>
-      <c r="M80" s="196"/>
-      <c r="N80" s="196"/>
-      <c r="O80" s="196"/>
-      <c r="P80" s="196"/>
-      <c r="Q80" s="196"/>
-      <c r="R80" s="196"/>
-      <c r="S80" s="196"/>
-      <c r="T80" s="196"/>
-      <c r="U80" s="196"/>
+      <c r="D80" s="125"/>
+      <c r="E80" s="125"/>
+      <c r="F80" s="125"/>
+      <c r="G80" s="125"/>
+      <c r="H80" s="125"/>
+      <c r="I80" s="125"/>
+      <c r="J80" s="125"/>
+      <c r="K80" s="125"/>
+      <c r="L80" s="125"/>
+      <c r="M80" s="125"/>
+      <c r="N80" s="125"/>
+      <c r="O80" s="125"/>
+      <c r="P80" s="125"/>
+      <c r="Q80" s="125"/>
+      <c r="R80" s="125"/>
+      <c r="S80" s="125"/>
+      <c r="T80" s="125"/>
+      <c r="U80" s="125"/>
     </row>
     <row r="81" spans="2:21" ht="40" customHeight="1">
-      <c r="C81" s="196" t="s">
-        <v>123</v>
+      <c r="C81" s="125" t="s">
+        <v>114</v>
       </c>
-      <c r="D81" s="196"/>
-      <c r="E81" s="196"/>
-      <c r="F81" s="196"/>
-      <c r="G81" s="196"/>
-      <c r="H81" s="196"/>
-      <c r="I81" s="196"/>
-      <c r="J81" s="196"/>
-      <c r="K81" s="196"/>
-      <c r="L81" s="196"/>
-      <c r="M81" s="196"/>
-      <c r="N81" s="196"/>
-      <c r="O81" s="196"/>
-      <c r="P81" s="196"/>
-      <c r="Q81" s="196"/>
-      <c r="R81" s="196"/>
-      <c r="S81" s="196"/>
-      <c r="T81" s="196"/>
-      <c r="U81" s="196"/>
+      <c r="D81" s="125"/>
+      <c r="E81" s="125"/>
+      <c r="F81" s="125"/>
+      <c r="G81" s="125"/>
+      <c r="H81" s="125"/>
+      <c r="I81" s="125"/>
+      <c r="J81" s="125"/>
+      <c r="K81" s="125"/>
+      <c r="L81" s="125"/>
+      <c r="M81" s="125"/>
+      <c r="N81" s="125"/>
+      <c r="O81" s="125"/>
+      <c r="P81" s="125"/>
+      <c r="Q81" s="125"/>
+      <c r="R81" s="125"/>
+      <c r="S81" s="125"/>
+      <c r="T81" s="125"/>
+      <c r="U81" s="125"/>
     </row>
     <row r="82" spans="2:21" ht="20" customHeight="1">
       <c r="B82" s="26"/>
@@ -35915,7 +35955,7 @@
     </row>
     <row r="83" spans="2:21" ht="20" customHeight="1">
       <c r="B83" s="197" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C83" s="198"/>
       <c r="D83" s="198"/>
@@ -35927,50 +35967,50 @@
       <c r="J83" s="198"/>
     </row>
     <row r="84" spans="2:21" ht="54.75" customHeight="1">
-      <c r="C84" s="196" t="s">
-        <v>158</v>
+      <c r="C84" s="125" t="s">
+        <v>142</v>
       </c>
-      <c r="D84" s="196"/>
-      <c r="E84" s="196"/>
-      <c r="F84" s="196"/>
-      <c r="G84" s="196"/>
-      <c r="H84" s="196"/>
-      <c r="I84" s="196"/>
-      <c r="J84" s="196"/>
-      <c r="K84" s="196"/>
-      <c r="L84" s="196"/>
-      <c r="M84" s="196"/>
-      <c r="N84" s="196"/>
-      <c r="O84" s="196"/>
-      <c r="P84" s="196"/>
-      <c r="Q84" s="196"/>
-      <c r="R84" s="196"/>
-      <c r="S84" s="196"/>
-      <c r="T84" s="196"/>
-      <c r="U84" s="196"/>
+      <c r="D84" s="125"/>
+      <c r="E84" s="125"/>
+      <c r="F84" s="125"/>
+      <c r="G84" s="125"/>
+      <c r="H84" s="125"/>
+      <c r="I84" s="125"/>
+      <c r="J84" s="125"/>
+      <c r="K84" s="125"/>
+      <c r="L84" s="125"/>
+      <c r="M84" s="125"/>
+      <c r="N84" s="125"/>
+      <c r="O84" s="125"/>
+      <c r="P84" s="125"/>
+      <c r="Q84" s="125"/>
+      <c r="R84" s="125"/>
+      <c r="S84" s="125"/>
+      <c r="T84" s="125"/>
+      <c r="U84" s="125"/>
     </row>
     <row r="85" spans="2:21" ht="40" customHeight="1">
-      <c r="C85" s="196" t="s">
-        <v>159</v>
+      <c r="C85" s="125" t="s">
+        <v>143</v>
       </c>
-      <c r="D85" s="196"/>
-      <c r="E85" s="196"/>
-      <c r="F85" s="196"/>
-      <c r="G85" s="196"/>
-      <c r="H85" s="196"/>
-      <c r="I85" s="196"/>
-      <c r="J85" s="196"/>
-      <c r="K85" s="196"/>
-      <c r="L85" s="196"/>
-      <c r="M85" s="196"/>
-      <c r="N85" s="196"/>
-      <c r="O85" s="196"/>
-      <c r="P85" s="196"/>
-      <c r="Q85" s="196"/>
-      <c r="R85" s="196"/>
-      <c r="S85" s="196"/>
-      <c r="T85" s="196"/>
-      <c r="U85" s="196"/>
+      <c r="D85" s="125"/>
+      <c r="E85" s="125"/>
+      <c r="F85" s="125"/>
+      <c r="G85" s="125"/>
+      <c r="H85" s="125"/>
+      <c r="I85" s="125"/>
+      <c r="J85" s="125"/>
+      <c r="K85" s="125"/>
+      <c r="L85" s="125"/>
+      <c r="M85" s="125"/>
+      <c r="N85" s="125"/>
+      <c r="O85" s="125"/>
+      <c r="P85" s="125"/>
+      <c r="Q85" s="125"/>
+      <c r="R85" s="125"/>
+      <c r="S85" s="125"/>
+      <c r="T85" s="125"/>
+      <c r="U85" s="125"/>
     </row>
     <row r="86" spans="2:21" ht="20" customHeight="1">
       <c r="B86" s="26"/>
@@ -35980,7 +36020,7 @@
     </row>
     <row r="87" spans="2:21" ht="20" customHeight="1">
       <c r="B87" s="197" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C87" s="198"/>
       <c r="D87" s="198"/>
@@ -35993,51 +36033,51 @@
     </row>
     <row r="88" spans="2:21" ht="40" customHeight="1">
       <c r="B88" s="29"/>
-      <c r="C88" s="196" t="s">
-        <v>134</v>
+      <c r="C88" s="125" t="s">
+        <v>125</v>
       </c>
-      <c r="D88" s="196"/>
-      <c r="E88" s="196"/>
-      <c r="F88" s="196"/>
-      <c r="G88" s="196"/>
-      <c r="H88" s="196"/>
-      <c r="I88" s="196"/>
-      <c r="J88" s="196"/>
-      <c r="K88" s="196"/>
-      <c r="L88" s="196"/>
-      <c r="M88" s="196"/>
-      <c r="N88" s="196"/>
-      <c r="O88" s="196"/>
-      <c r="P88" s="196"/>
-      <c r="Q88" s="196"/>
-      <c r="R88" s="196"/>
-      <c r="S88" s="196"/>
-      <c r="T88" s="196"/>
-      <c r="U88" s="196"/>
+      <c r="D88" s="125"/>
+      <c r="E88" s="125"/>
+      <c r="F88" s="125"/>
+      <c r="G88" s="125"/>
+      <c r="H88" s="125"/>
+      <c r="I88" s="125"/>
+      <c r="J88" s="125"/>
+      <c r="K88" s="125"/>
+      <c r="L88" s="125"/>
+      <c r="M88" s="125"/>
+      <c r="N88" s="125"/>
+      <c r="O88" s="125"/>
+      <c r="P88" s="125"/>
+      <c r="Q88" s="125"/>
+      <c r="R88" s="125"/>
+      <c r="S88" s="125"/>
+      <c r="T88" s="125"/>
+      <c r="U88" s="125"/>
     </row>
     <row r="89" spans="2:21" ht="40" customHeight="1">
       <c r="B89" s="29"/>
-      <c r="C89" s="196" t="s">
-        <v>160</v>
+      <c r="C89" s="125" t="s">
+        <v>144</v>
       </c>
-      <c r="D89" s="196"/>
-      <c r="E89" s="196"/>
-      <c r="F89" s="196"/>
-      <c r="G89" s="196"/>
-      <c r="H89" s="196"/>
-      <c r="I89" s="196"/>
-      <c r="J89" s="196"/>
-      <c r="K89" s="196"/>
-      <c r="L89" s="196"/>
-      <c r="M89" s="196"/>
-      <c r="N89" s="196"/>
-      <c r="O89" s="196"/>
-      <c r="P89" s="196"/>
-      <c r="Q89" s="196"/>
-      <c r="R89" s="196"/>
-      <c r="S89" s="196"/>
-      <c r="T89" s="196"/>
-      <c r="U89" s="196"/>
+      <c r="D89" s="125"/>
+      <c r="E89" s="125"/>
+      <c r="F89" s="125"/>
+      <c r="G89" s="125"/>
+      <c r="H89" s="125"/>
+      <c r="I89" s="125"/>
+      <c r="J89" s="125"/>
+      <c r="K89" s="125"/>
+      <c r="L89" s="125"/>
+      <c r="M89" s="125"/>
+      <c r="N89" s="125"/>
+      <c r="O89" s="125"/>
+      <c r="P89" s="125"/>
+      <c r="Q89" s="125"/>
+      <c r="R89" s="125"/>
+      <c r="S89" s="125"/>
+      <c r="T89" s="125"/>
+      <c r="U89" s="125"/>
     </row>
     <row r="90" spans="2:21" ht="20" customHeight="1">
       <c r="B90" s="26"/>
@@ -36047,7 +36087,7 @@
     </row>
     <row r="91" spans="2:21" ht="20" customHeight="1">
       <c r="B91" s="197" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C91" s="197"/>
       <c r="D91" s="197"/>
@@ -36059,27 +36099,27 @@
       <c r="J91" s="197"/>
     </row>
     <row r="92" spans="2:21" ht="40" customHeight="1">
-      <c r="C92" s="196" t="s">
-        <v>135</v>
+      <c r="C92" s="125" t="s">
+        <v>126</v>
       </c>
-      <c r="D92" s="196"/>
-      <c r="E92" s="196"/>
-      <c r="F92" s="196"/>
-      <c r="G92" s="196"/>
-      <c r="H92" s="196"/>
-      <c r="I92" s="196"/>
-      <c r="J92" s="196"/>
-      <c r="K92" s="196"/>
-      <c r="L92" s="196"/>
-      <c r="M92" s="196"/>
-      <c r="N92" s="196"/>
-      <c r="O92" s="196"/>
-      <c r="P92" s="196"/>
-      <c r="Q92" s="196"/>
-      <c r="R92" s="196"/>
-      <c r="S92" s="196"/>
-      <c r="T92" s="196"/>
-      <c r="U92" s="196"/>
+      <c r="D92" s="125"/>
+      <c r="E92" s="125"/>
+      <c r="F92" s="125"/>
+      <c r="G92" s="125"/>
+      <c r="H92" s="125"/>
+      <c r="I92" s="125"/>
+      <c r="J92" s="125"/>
+      <c r="K92" s="125"/>
+      <c r="L92" s="125"/>
+      <c r="M92" s="125"/>
+      <c r="N92" s="125"/>
+      <c r="O92" s="125"/>
+      <c r="P92" s="125"/>
+      <c r="Q92" s="125"/>
+      <c r="R92" s="125"/>
+      <c r="S92" s="125"/>
+      <c r="T92" s="125"/>
+      <c r="U92" s="125"/>
     </row>
     <row r="93" spans="2:21" ht="20" customHeight="1">
       <c r="B93" s="26"/>
@@ -36089,7 +36129,7 @@
     </row>
     <row r="94" spans="2:21" ht="20" customHeight="1">
       <c r="B94" s="117" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C94" s="28"/>
       <c r="D94" s="28"/>
@@ -36102,7 +36142,7 @@
     </row>
     <row r="95" spans="2:21" ht="20" customHeight="1">
       <c r="C95" s="199" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D95" s="199"/>
       <c r="E95" s="199"/>
@@ -36125,99 +36165,99 @@
     </row>
     <row r="96" spans="2:21" ht="20" customHeight="1">
       <c r="B96" s="30"/>
-      <c r="C96" s="195" t="s">
-        <v>133</v>
+      <c r="C96" s="202" t="s">
+        <v>124</v>
       </c>
-      <c r="D96" s="195"/>
-      <c r="E96" s="195"/>
-      <c r="F96" s="195"/>
-      <c r="G96" s="195"/>
-      <c r="H96" s="195"/>
-      <c r="I96" s="195"/>
-      <c r="J96" s="195"/>
-      <c r="K96" s="195"/>
-      <c r="L96" s="195"/>
-      <c r="M96" s="195"/>
-      <c r="N96" s="195"/>
-      <c r="O96" s="195"/>
-      <c r="P96" s="195"/>
-      <c r="Q96" s="195"/>
-      <c r="R96" s="195"/>
-      <c r="S96" s="195"/>
-      <c r="T96" s="195"/>
-      <c r="U96" s="195"/>
+      <c r="D96" s="202"/>
+      <c r="E96" s="202"/>
+      <c r="F96" s="202"/>
+      <c r="G96" s="202"/>
+      <c r="H96" s="202"/>
+      <c r="I96" s="202"/>
+      <c r="J96" s="202"/>
+      <c r="K96" s="202"/>
+      <c r="L96" s="202"/>
+      <c r="M96" s="202"/>
+      <c r="N96" s="202"/>
+      <c r="O96" s="202"/>
+      <c r="P96" s="202"/>
+      <c r="Q96" s="202"/>
+      <c r="R96" s="202"/>
+      <c r="S96" s="202"/>
+      <c r="T96" s="202"/>
+      <c r="U96" s="202"/>
     </row>
     <row r="97" spans="2:21" ht="20" customHeight="1">
       <c r="B97" s="30"/>
-      <c r="C97" s="195" t="s">
-        <v>132</v>
+      <c r="C97" s="202" t="s">
+        <v>123</v>
       </c>
-      <c r="D97" s="195"/>
-      <c r="E97" s="195"/>
-      <c r="F97" s="195"/>
-      <c r="G97" s="195"/>
-      <c r="H97" s="195"/>
-      <c r="I97" s="195"/>
-      <c r="J97" s="195"/>
-      <c r="K97" s="195"/>
-      <c r="L97" s="195"/>
-      <c r="M97" s="195"/>
-      <c r="N97" s="195"/>
-      <c r="O97" s="195"/>
-      <c r="P97" s="195"/>
-      <c r="Q97" s="195"/>
-      <c r="R97" s="195"/>
-      <c r="S97" s="195"/>
-      <c r="T97" s="195"/>
-      <c r="U97" s="195"/>
+      <c r="D97" s="202"/>
+      <c r="E97" s="202"/>
+      <c r="F97" s="202"/>
+      <c r="G97" s="202"/>
+      <c r="H97" s="202"/>
+      <c r="I97" s="202"/>
+      <c r="J97" s="202"/>
+      <c r="K97" s="202"/>
+      <c r="L97" s="202"/>
+      <c r="M97" s="202"/>
+      <c r="N97" s="202"/>
+      <c r="O97" s="202"/>
+      <c r="P97" s="202"/>
+      <c r="Q97" s="202"/>
+      <c r="R97" s="202"/>
+      <c r="S97" s="202"/>
+      <c r="T97" s="202"/>
+      <c r="U97" s="202"/>
     </row>
     <row r="98" spans="2:21" ht="20" customHeight="1">
       <c r="B98" s="30"/>
-      <c r="C98" s="195" t="s">
-        <v>47</v>
+      <c r="C98" s="202" t="s">
+        <v>44</v>
       </c>
-      <c r="D98" s="195"/>
-      <c r="E98" s="195"/>
-      <c r="F98" s="195"/>
-      <c r="G98" s="195"/>
-      <c r="H98" s="195"/>
-      <c r="I98" s="195"/>
-      <c r="J98" s="195"/>
-      <c r="K98" s="195"/>
-      <c r="L98" s="195"/>
-      <c r="M98" s="195"/>
-      <c r="N98" s="195"/>
-      <c r="O98" s="195"/>
-      <c r="P98" s="195"/>
-      <c r="Q98" s="195"/>
-      <c r="R98" s="195"/>
-      <c r="S98" s="195"/>
-      <c r="T98" s="195"/>
-      <c r="U98" s="195"/>
+      <c r="D98" s="202"/>
+      <c r="E98" s="202"/>
+      <c r="F98" s="202"/>
+      <c r="G98" s="202"/>
+      <c r="H98" s="202"/>
+      <c r="I98" s="202"/>
+      <c r="J98" s="202"/>
+      <c r="K98" s="202"/>
+      <c r="L98" s="202"/>
+      <c r="M98" s="202"/>
+      <c r="N98" s="202"/>
+      <c r="O98" s="202"/>
+      <c r="P98" s="202"/>
+      <c r="Q98" s="202"/>
+      <c r="R98" s="202"/>
+      <c r="S98" s="202"/>
+      <c r="T98" s="202"/>
+      <c r="U98" s="202"/>
     </row>
     <row r="99" spans="2:21" ht="20" customHeight="1">
       <c r="B99" s="30"/>
-      <c r="C99" s="195" t="s">
-        <v>48</v>
+      <c r="C99" s="202" t="s">
+        <v>45</v>
       </c>
-      <c r="D99" s="195"/>
-      <c r="E99" s="195"/>
-      <c r="F99" s="195"/>
-      <c r="G99" s="195"/>
-      <c r="H99" s="195"/>
-      <c r="I99" s="195"/>
-      <c r="J99" s="195"/>
-      <c r="K99" s="195"/>
-      <c r="L99" s="195"/>
-      <c r="M99" s="195"/>
-      <c r="N99" s="195"/>
-      <c r="O99" s="195"/>
-      <c r="P99" s="195"/>
-      <c r="Q99" s="195"/>
-      <c r="R99" s="195"/>
-      <c r="S99" s="195"/>
-      <c r="T99" s="195"/>
-      <c r="U99" s="195"/>
+      <c r="D99" s="202"/>
+      <c r="E99" s="202"/>
+      <c r="F99" s="202"/>
+      <c r="G99" s="202"/>
+      <c r="H99" s="202"/>
+      <c r="I99" s="202"/>
+      <c r="J99" s="202"/>
+      <c r="K99" s="202"/>
+      <c r="L99" s="202"/>
+      <c r="M99" s="202"/>
+      <c r="N99" s="202"/>
+      <c r="O99" s="202"/>
+      <c r="P99" s="202"/>
+      <c r="Q99" s="202"/>
+      <c r="R99" s="202"/>
+      <c r="S99" s="202"/>
+      <c r="T99" s="202"/>
+      <c r="U99" s="202"/>
     </row>
     <row r="100" spans="2:21" ht="20" customHeight="1">
       <c r="B100" s="26"/>
@@ -36227,7 +36267,7 @@
     </row>
     <row r="101" spans="2:21" ht="20" customHeight="1">
       <c r="B101" s="117" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C101" s="28"/>
       <c r="D101" s="28"/>
@@ -36239,27 +36279,27 @@
       <c r="J101" s="28"/>
     </row>
     <row r="102" spans="2:21" ht="40" customHeight="1">
-      <c r="C102" s="196" t="s">
-        <v>131</v>
+      <c r="C102" s="125" t="s">
+        <v>122</v>
       </c>
-      <c r="D102" s="196"/>
-      <c r="E102" s="196"/>
-      <c r="F102" s="196"/>
-      <c r="G102" s="196"/>
-      <c r="H102" s="196"/>
-      <c r="I102" s="196"/>
-      <c r="J102" s="196"/>
-      <c r="K102" s="196"/>
-      <c r="L102" s="196"/>
-      <c r="M102" s="196"/>
-      <c r="N102" s="196"/>
-      <c r="O102" s="196"/>
-      <c r="P102" s="196"/>
-      <c r="Q102" s="196"/>
-      <c r="R102" s="196"/>
-      <c r="S102" s="196"/>
-      <c r="T102" s="196"/>
-      <c r="U102" s="196"/>
+      <c r="D102" s="125"/>
+      <c r="E102" s="125"/>
+      <c r="F102" s="125"/>
+      <c r="G102" s="125"/>
+      <c r="H102" s="125"/>
+      <c r="I102" s="125"/>
+      <c r="J102" s="125"/>
+      <c r="K102" s="125"/>
+      <c r="L102" s="125"/>
+      <c r="M102" s="125"/>
+      <c r="N102" s="125"/>
+      <c r="O102" s="125"/>
+      <c r="P102" s="125"/>
+      <c r="Q102" s="125"/>
+      <c r="R102" s="125"/>
+      <c r="S102" s="125"/>
+      <c r="T102" s="125"/>
+      <c r="U102" s="125"/>
     </row>
     <row r="103" spans="2:21" ht="20" customHeight="1">
       <c r="B103" s="26"/>
@@ -36269,7 +36309,7 @@
     </row>
     <row r="104" spans="2:21" ht="20" customHeight="1">
       <c r="B104" s="197" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C104" s="198"/>
       <c r="D104" s="198"/>
@@ -36281,29 +36321,29 @@
       <c r="J104" s="198"/>
     </row>
     <row r="105" spans="2:21" ht="40" customHeight="1">
-      <c r="C105" s="196" t="s">
-        <v>49</v>
+      <c r="C105" s="125" t="s">
+        <v>46</v>
       </c>
-      <c r="D105" s="196"/>
-      <c r="E105" s="196"/>
-      <c r="F105" s="196"/>
-      <c r="G105" s="196"/>
-      <c r="H105" s="196"/>
-      <c r="I105" s="196"/>
-      <c r="J105" s="196"/>
-      <c r="K105" s="196"/>
-      <c r="L105" s="196"/>
-      <c r="M105" s="196"/>
-      <c r="N105" s="196"/>
-      <c r="O105" s="196"/>
-      <c r="P105" s="196"/>
-      <c r="Q105" s="196"/>
-      <c r="R105" s="196"/>
-      <c r="S105" s="196"/>
-      <c r="T105" s="196"/>
-      <c r="U105" s="196"/>
-    </row>
-    <row r="106" spans="2:21" ht="328.5" customHeight="1"/>
+      <c r="D105" s="125"/>
+      <c r="E105" s="125"/>
+      <c r="F105" s="125"/>
+      <c r="G105" s="125"/>
+      <c r="H105" s="125"/>
+      <c r="I105" s="125"/>
+      <c r="J105" s="125"/>
+      <c r="K105" s="125"/>
+      <c r="L105" s="125"/>
+      <c r="M105" s="125"/>
+      <c r="N105" s="125"/>
+      <c r="O105" s="125"/>
+      <c r="P105" s="125"/>
+      <c r="Q105" s="125"/>
+      <c r="R105" s="125"/>
+      <c r="S105" s="125"/>
+      <c r="T105" s="125"/>
+      <c r="U105" s="125"/>
+    </row>
+    <row r="106" spans="2:21" ht="337" customHeight="1"/>
     <row r="107" spans="2:21" ht="25" customHeight="1"/>
     <row r="108" spans="2:21" ht="25" customHeight="1"/>
     <row r="109" spans="2:21" ht="25" customHeight="1"/>
@@ -36311,6 +36351,88 @@
     <row r="111" spans="2:21" ht="25" customHeight="1"/>
   </sheetData>
   <mergeCells count="98">
+    <mergeCell ref="B83:J83"/>
+    <mergeCell ref="B79:J79"/>
+    <mergeCell ref="C80:U80"/>
+    <mergeCell ref="B91:J91"/>
+    <mergeCell ref="C84:U84"/>
+    <mergeCell ref="C85:U85"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="C88:U88"/>
+    <mergeCell ref="C89:U89"/>
+    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="C105:U105"/>
+    <mergeCell ref="C92:U92"/>
+    <mergeCell ref="C95:U95"/>
+    <mergeCell ref="C96:U96"/>
+    <mergeCell ref="C97:U97"/>
+    <mergeCell ref="C98:U98"/>
+    <mergeCell ref="C99:U99"/>
+    <mergeCell ref="C102:U102"/>
+    <mergeCell ref="C81:U81"/>
+    <mergeCell ref="B72:J72"/>
+    <mergeCell ref="C74:U74"/>
+    <mergeCell ref="B76:J76"/>
+    <mergeCell ref="C77:U77"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="C64:U64"/>
+    <mergeCell ref="B66:U66"/>
+    <mergeCell ref="C69:U69"/>
+    <mergeCell ref="B56:U56"/>
+    <mergeCell ref="B57:U57"/>
+    <mergeCell ref="C59:U59"/>
+    <mergeCell ref="C60:U60"/>
+    <mergeCell ref="C61:U61"/>
+    <mergeCell ref="C67:U67"/>
+    <mergeCell ref="C68:U68"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="E54:K54"/>
+    <mergeCell ref="L54:N54"/>
+    <mergeCell ref="O54:U54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="E55:K55"/>
+    <mergeCell ref="L55:N55"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="E53:K53"/>
+    <mergeCell ref="L53:N53"/>
+    <mergeCell ref="O53:U53"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:U47"/>
+    <mergeCell ref="E48:U48"/>
+    <mergeCell ref="E49:U49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="E51:U51"/>
+    <mergeCell ref="B52:K52"/>
+    <mergeCell ref="L52:U52"/>
+    <mergeCell ref="B45:U45"/>
+    <mergeCell ref="G38:U38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G39:U39"/>
+    <mergeCell ref="D40:F41"/>
+    <mergeCell ref="G40:U40"/>
+    <mergeCell ref="B35:C43"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:U36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G37:U37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:U42"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="G31:U31"/>
+    <mergeCell ref="G32:U32"/>
+    <mergeCell ref="G33:U33"/>
+    <mergeCell ref="G34:U34"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="G43:U43"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:M41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:U41"/>
+    <mergeCell ref="G35:U35"/>
     <mergeCell ref="W64:AO64"/>
     <mergeCell ref="B7:U7"/>
     <mergeCell ref="B8:U8"/>
@@ -36327,92 +36449,10 @@
     <mergeCell ref="G29:U29"/>
     <mergeCell ref="D30:F34"/>
     <mergeCell ref="G30:U30"/>
-    <mergeCell ref="G31:U31"/>
-    <mergeCell ref="G32:U32"/>
-    <mergeCell ref="G33:U33"/>
-    <mergeCell ref="G34:U34"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="G43:U43"/>
-    <mergeCell ref="G35:L35"/>
-    <mergeCell ref="M35:S35"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:M41"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:U41"/>
-    <mergeCell ref="B45:U45"/>
-    <mergeCell ref="G38:U38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G39:U39"/>
-    <mergeCell ref="D40:F41"/>
-    <mergeCell ref="G40:U40"/>
-    <mergeCell ref="B35:C43"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:U36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G37:U37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G42:U42"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="E53:K53"/>
-    <mergeCell ref="L53:N53"/>
-    <mergeCell ref="O53:U53"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:U47"/>
-    <mergeCell ref="E48:U48"/>
-    <mergeCell ref="E49:U49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="E51:U51"/>
-    <mergeCell ref="B52:K52"/>
-    <mergeCell ref="L52:U52"/>
-    <mergeCell ref="B56:U56"/>
-    <mergeCell ref="B57:U57"/>
-    <mergeCell ref="B59:U59"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="E54:K54"/>
-    <mergeCell ref="L54:N54"/>
-    <mergeCell ref="O54:U54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="E55:K55"/>
-    <mergeCell ref="L55:N55"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="B72:J72"/>
-    <mergeCell ref="C74:U74"/>
-    <mergeCell ref="B76:J76"/>
-    <mergeCell ref="C77:U77"/>
-    <mergeCell ref="B61:U61"/>
-    <mergeCell ref="B63:J63"/>
-    <mergeCell ref="C64:U64"/>
-    <mergeCell ref="B66:U66"/>
-    <mergeCell ref="F67:U67"/>
-    <mergeCell ref="J60:U60"/>
-    <mergeCell ref="B83:J83"/>
-    <mergeCell ref="B79:J79"/>
-    <mergeCell ref="C80:U80"/>
-    <mergeCell ref="C81:U81"/>
-    <mergeCell ref="B91:J91"/>
-    <mergeCell ref="C84:U84"/>
-    <mergeCell ref="C85:U85"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="C88:U88"/>
-    <mergeCell ref="C89:U89"/>
-    <mergeCell ref="C99:U99"/>
-    <mergeCell ref="C102:U102"/>
-    <mergeCell ref="B104:J104"/>
-    <mergeCell ref="C105:U105"/>
-    <mergeCell ref="C92:U92"/>
-    <mergeCell ref="C95:U95"/>
-    <mergeCell ref="C96:U96"/>
-    <mergeCell ref="C97:U97"/>
-    <mergeCell ref="C98:U98"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="27" min="1" max="20" man="1"/>

--- a/repair/back/doc/estimate/defect.xlsx
+++ b/repair/back/doc/estimate/defect.xlsx
@@ -1426,7 +1426,7 @@
     <numFmt numFmtId="244" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="245" formatCode="0_ "/>
   </numFmts>
-  <fonts count="169">
+  <fonts count="159">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -1725,11 +1725,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="1.0"/>
-      <name val="Courier"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="돋움체"/>
       <color rgb="FF000000"/>
@@ -1796,11 +1791,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="바탕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="한컴 솔잎 B"/>
       <color rgb="FF000000"/>
@@ -1856,16 +1846,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="한컴 솔잎 B"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="11.0"/>
       <name val="한컴 솔잎 B"/>
@@ -1908,11 +1888,6 @@
     <font>
       <b/>
       <sz val="36.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
       <name val="돋움"/>
       <color rgb="FF000000"/>
     </font>
@@ -1999,17 +1974,6 @@
       <b/>
       <sz val="14.0"/>
       <name val="MS Gothic"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="돋움"/>
       <color rgb="FF000000"/>
     </font>
     <font>
@@ -2126,12 +2090,6 @@
       <color rgb="FFFA7D00"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color theme="1"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="돋움"/>
       <color rgb="FF006100"/>
@@ -2191,16 +2149,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <color theme="1"/>
@@ -2225,11 +2173,6 @@
     </font>
     <font>
       <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
@@ -2264,12 +2207,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
       <sz val="32.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
@@ -2290,22 +2227,12 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="9.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
     <font>
       <sz val="16.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="13.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
@@ -2338,8 +2265,29 @@
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
+    <font>
+      <sz val="16.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24.0"/>
+      <name val="바탕"/>
+      <color rgb="FF000000"/>
+    </font>
   </fonts>
-  <fills count="43">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2412,12 +2360,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.150000"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3500,7 +3442,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3509,7 +3450,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3518,7 +3458,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3527,7 +3466,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -3542,7 +3480,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -3557,7 +3494,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -3572,7 +3508,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3581,7 +3516,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3592,7 +3526,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3167">
@@ -11511,7 +11444,7 @@
     <xf numFmtId="2" fontId="16" fillId="0" borderId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="82" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="197" fontId="19" fillId="0" borderId="0">
@@ -11950,7 +11883,7 @@
     <xf numFmtId="10" fontId="55" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -11972,34 +11905,34 @@
     <xf numFmtId="226" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="227" fontId="58" fillId="0" borderId="14" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="227" fontId="57" fillId="0" borderId="14" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="60" fillId="0" borderId="11">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="59" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="15">
+    <xf numFmtId="179" fontId="60" fillId="0" borderId="15">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="228" fontId="55" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="190" fontId="62" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="229" fontId="63" fillId="0" borderId="0">
+    <xf numFmtId="190" fontId="61" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="229" fontId="62" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -12788,43 +12721,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="16">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="16">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="230" fontId="32" fillId="0" borderId="2" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="231" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="231" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
@@ -12839,20 +12772,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -12880,7 +12813,7 @@
     <xf numFmtId="38" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="228" fontId="57" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="228" fontId="56" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="235" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -12889,7 +12822,7 @@
     <xf numFmtId="236" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="237" fontId="57" fillId="0" borderId="2">
+    <xf numFmtId="237" fontId="56" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="238" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -12901,11 +12834,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -12916,17 +12849,17 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15">
       <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18">
@@ -12950,7 +12883,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -12977,10 +12910,10 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="2" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="2" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -13010,133 +12943,133 @@
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="77" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="78" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="79" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="80" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="14" borderId="81" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="15" borderId="82" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="15" borderId="81" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="16" borderId="83" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="84" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="85" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="35" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="36" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="39" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="40" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="42" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="77" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="78" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="79" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="80" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="13" borderId="81" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="14" borderId="82" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="14" borderId="81" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="15" borderId="83" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="84" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="85" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="35" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="36" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="39" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="40" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -13152,76 +13085,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="84" fillId="2" borderId="2" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="80" fillId="2" borderId="2" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="84" fillId="2" borderId="2" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="80" fillId="2" borderId="2" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="34" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="34" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="36" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="36" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="75" fillId="0" borderId="38" xfId="2792" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="73" fillId="0" borderId="38" xfId="2792" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="75" fillId="0" borderId="38" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="73" fillId="0" borderId="38" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="75" fillId="0" borderId="40" xfId="2792" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="73" fillId="0" borderId="40" xfId="2792" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="42" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="42" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="11" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="11" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="8" borderId="52" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="52" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="75" fillId="0" borderId="28" xfId="2792" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="73" fillId="0" borderId="28" xfId="2792" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -13230,22 +13163,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="2" xfId="3114">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="3113" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="17" xfId="3114" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="17" xfId="3113" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="0" xfId="3114" applyBorder="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="2" xfId="3114">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="3113" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="17" xfId="3114" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="17" xfId="3113" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="0" xfId="3114" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3113">
@@ -13257,10 +13190,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="8" xfId="3113" applyBorder="1">
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="8" xfId="3113" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3113" applyBorder="1">
@@ -13269,25 +13202,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113">
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="3113">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="3113" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="12" borderId="0" xfId="3113" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="97" fillId="12" borderId="0" xfId="3113" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="33" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="33" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="243" fontId="78" fillId="0" borderId="8" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="243" fontId="76" fillId="0" borderId="8" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
@@ -13296,169 +13229,169 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="2" borderId="36" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="69" fillId="2" borderId="36" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="35" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="75" fillId="0" borderId="37" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="35" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="73" fillId="0" borderId="37" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="29" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="29" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="75" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="73" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="40" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="40" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="72" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="39" xfId="3102" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="39" xfId="3102" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="41" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="41" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="43" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="43" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="44" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="44" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="75" fillId="0" borderId="38" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="73" fillId="0" borderId="38" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="30" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="30" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="45" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="45" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="75" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="73" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="244" fontId="75" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="244" fontId="73" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="244" fontId="75" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="244" fontId="73" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="48" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="48" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="46" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="75" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="46" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="73" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="244" fontId="75" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="244" fontId="73" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="84" fillId="2" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="80" fillId="2" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="69" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="8" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="69" fillId="8" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="8" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="69" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="72" fillId="8" borderId="8" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="70" fillId="8" borderId="8" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="51" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="51" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="23" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="23" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="25" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="25" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="27" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="27" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3102"/>
@@ -13468,398 +13401,404 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="76" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="107" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="107" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="245" fontId="101" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="21" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="22" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="24" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="0" xfId="3102" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="26" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="22" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="49" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="7" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="75" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="49" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="7" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="68" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="69" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="7" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="7" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="68" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="69" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="70" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="71" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="6" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="54" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="71" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="72" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="59" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="60" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="76" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="92" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="114" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="114" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="245" fontId="106" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="21" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="22" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="24" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="0" xfId="3102" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="26" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="22" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="49" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="7" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="75" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="49" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="7" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="68" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="69" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="7" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="7" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="68" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="69" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="70" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="71" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="6" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="54" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="71" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="72" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="59" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="60" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="2" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13868,52 +13807,46 @@
     <xf numFmtId="0" fontId="71" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="2" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="75" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="75" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="71" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="71" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="72" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="72" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="72" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="70" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="72" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="70" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="72" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="70" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="7" borderId="59" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="7" borderId="59" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="7" borderId="60" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="7" borderId="60" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -17251,7 +17184,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="0" y="8281035"/>
-            <a:ext cx="3175" cy="0"/>
+            <a:ext cx="0" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="rect"/>
           <a:noFill/>
@@ -17299,7 +17232,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="0" y="8281035"/>
-            <a:ext cx="3175" cy="0"/>
+            <a:ext cx="0" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="rect"/>
           <a:noFill/>
@@ -17347,7 +17280,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="0" y="8281035"/>
-            <a:ext cx="3175" cy="0"/>
+            <a:ext cx="0" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="rect"/>
           <a:noFill/>
@@ -17408,7 +17341,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="0" y="8281035"/>
-            <a:ext cx="3175" cy="0"/>
+            <a:ext cx="0" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="rect"/>
           <a:noFill/>
@@ -18376,22 +18309,6 @@
       <c r="K9" s="38"/>
       <c r="L9" s="38"/>
       <c r="M9" s="38"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="37"/>
     </row>
     <row r="10" spans="2:29" s="37" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B10" s="200" t="s">
@@ -18793,7 +18710,6 @@
       <c r="R22" s="115"/>
       <c r="S22" s="115"/>
       <c r="T22" s="115"/>
-      <c r="U22" s="37"/>
       <c r="V22" s="115"/>
       <c r="W22" s="115"/>
       <c r="X22" s="115"/>
@@ -36393,8 +36309,8 @@
     <mergeCell ref="B18:AC18"/>
     <mergeCell ref="B20:K20"/>
     <mergeCell ref="F21:K21"/>
+    <mergeCell ref="F22:K22"/>
     <mergeCell ref="F23:K23"/>
-    <mergeCell ref="F22:K22"/>
     <mergeCell ref="F24:K24"/>
     <mergeCell ref="F25:K25"/>
     <mergeCell ref="B27:K27"/>
@@ -36487,9 +36403,9 @@
         <v>58</v>
       </c>
       <c r="C5" s="232"/>
-      <c r="D5" s="233" t="e">
+      <c r="D5" s="233">
         <f>"일금 "&amp;NUMBERSTRING(H30,1)&amp;"원정"&amp;TEXT(H30,"(￦ #,##0)")&amp;" "</f>
-        <v>일금 #VALUE!원정</v>
+        <v/>
       </c>
       <c r="E5" s="234"/>
       <c r="F5" s="234"/>
@@ -38790,7 +38706,7 @@
     </row>
     <row r="68" spans="2:21" ht="20.000000" customHeight="1">
       <c r="C68" s="28" t="str">
-        <f>"② 위      치 : "&amp;E54</f>
+        <f>"② 위      치 : "&amp;갑지!L22</f>
         <v>② 위      치 : 인천 계양구 아나지로 199 (효성동)</v>
       </c>
       <c r="D68" s="28"/>
